--- a/Assignment 3 - Text , Logical, Date, Sumifs etc...xlsx
+++ b/Assignment 3 - Text , Logical, Date, Sumifs etc...xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shaik\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Desktop\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BAFBFB-9015-4F34-875A-3F7F58BE6D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95AC37F8-5294-47BF-8901-DF38A79ED50F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arithmatic Functions" sheetId="7" r:id="rId1"/>
@@ -21,29 +21,36 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IF AND OR nested'!$A$10:$N$48</definedName>
+    <definedName name="Basic_Salary" localSheetId="1">'IF AND OR nested'!$H$11:$H$48</definedName>
+    <definedName name="Basic_Salary">'Arithmatic Functions'!$J$7:$J$44</definedName>
+    <definedName name="Birthdate" localSheetId="1">'IF AND OR nested'!$D$11:$D$48</definedName>
+    <definedName name="Birthdate">'Arithmatic Functions'!$E$7:$E$44</definedName>
+    <definedName name="C_Code" localSheetId="1">'IF AND OR nested'!$A$11:$A$48</definedName>
+    <definedName name="C_Code">'Arithmatic Functions'!$B$7:$B$44</definedName>
+    <definedName name="Department" localSheetId="1">'IF AND OR nested'!$G$11:$G$48</definedName>
+    <definedName name="Department">'Arithmatic Functions'!$H$7:$H$44</definedName>
+    <definedName name="FirstName" localSheetId="1">'IF AND OR nested'!$B$11:$B$48</definedName>
+    <definedName name="FirstName">'Arithmatic Functions'!$C$7:$C$44</definedName>
+    <definedName name="Gender" localSheetId="1">'IF AND OR nested'!$E$11:$E$48</definedName>
+    <definedName name="Gender">'Arithmatic Functions'!$F$7:$F$44</definedName>
+    <definedName name="LastName" localSheetId="1">'IF AND OR nested'!$C$11:$C$48</definedName>
+    <definedName name="LastName">'Arithmatic Functions'!$D$7:$D$44</definedName>
+    <definedName name="M_Status" localSheetId="1">'IF AND OR nested'!$F$11:$F$48</definedName>
+    <definedName name="M_Status">'Arithmatic Functions'!$G$7:$G$44</definedName>
+    <definedName name="Region" localSheetId="1">'IF AND OR nested'!$I$11:$I$48</definedName>
+    <definedName name="Region">'Arithmatic Functions'!$I$7:$I$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="221">
   <si>
     <t>Full Name</t>
   </si>
@@ -295,9 +302,6 @@
   </si>
   <si>
     <t>Date (mm/dd/yyyy)</t>
-  </si>
-  <si>
-    <t>?</t>
   </si>
   <si>
     <t>VALIDATION SHEET</t>
@@ -707,17 +711,21 @@
   </si>
   <si>
     <t>Employees will receive TA-DA as per the Region they are posted in. North=5000, South=4000, East=4200, Midwest=3800</t>
+  </si>
+  <si>
+    <t>20070623</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -815,6 +823,13 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -995,11 +1010,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1020,7 +1036,6 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1041,7 +1056,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1053,6 +1068,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1063,7 +1090,8 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
@@ -1378,68 +1406,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:Q44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="49.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.21875" customWidth="1"/>
-    <col min="15" max="15" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C2" s="34" t="s">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C2" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="M2" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="M2" s="37" t="s">
+      <c r="N2" s="45"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C3" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="N2" s="38"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C3" s="34" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="M3" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="38">
+        <f>SUM(J7:J44)</f>
+        <v>2191000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M4" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="M4" s="5" t="s">
+      <c r="N4" s="37">
+        <f>AVERAGE(J7:J44)</f>
+        <v>57657.894736842107</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M5" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="37">
+        <f>MEDIAN(J7:J44)</f>
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>74</v>
@@ -1460,21 +1497,24 @@
         <v>59</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="N6" s="1">
+        <f>COUNTA(C7:C44)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>150834</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="E7" s="36">
         <v>31199</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -1489,25 +1529,28 @@
       <c r="I7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="37">
         <v>48000</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+      <c r="N7" s="37">
+        <f>MAX(J7:J44)</f>
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>150784</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="E8" s="36">
         <v>28365</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -1522,25 +1565,28 @@
       <c r="I8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="37">
         <v>35000</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+      <c r="N8" s="37">
+        <f>MIN(J7:J44)</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>150791</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="E9" s="36">
         <v>23346</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -1555,21 +1601,21 @@
       <c r="I9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="37">
         <v>67000</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>150940</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="E10" s="36">
         <v>26906</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -1584,25 +1630,25 @@
       <c r="I10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="37">
         <v>87000</v>
       </c>
-      <c r="M10" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="N10" s="38"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="M10" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="N10" s="45"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>150777</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="E11" s="36">
         <v>21123</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -1617,25 +1663,28 @@
       <c r="I11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="37">
         <v>22000</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="N11" s="1">
+        <f>COUNTIF(Gender,"male")</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>150805</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E12" s="4">
+        <v>148</v>
+      </c>
+      <c r="E12" s="36">
         <v>26172</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -1650,25 +1699,28 @@
       <c r="I12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="37">
         <v>91000</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+      <c r="N12" s="1">
+        <f>COUNTIF(Gender,"female")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <v>150990</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="E13" s="36">
         <v>36400</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -1683,25 +1735,28 @@
       <c r="I13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="37">
         <v>77000</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="N13" s="1">
+        <f>COUNTIF(Region,"north")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <v>150989</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E14" s="4">
+        <v>151</v>
+      </c>
+      <c r="E14" s="36">
         <v>33113</v>
       </c>
       <c r="F14" s="3" t="s">
@@ -1716,25 +1771,28 @@
       <c r="I14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="37">
         <v>45000</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+      <c r="N14" s="1">
+        <f>AVERAGEIF(Region,"north",Basic_Salary)</f>
+        <v>55700</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <v>150881</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="E15" s="36">
         <v>30337</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -1749,25 +1807,28 @@
       <c r="I15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="37">
         <v>92000</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="N15" s="1"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+      <c r="N15" s="1">
+        <f>_xlfn.MAXIFS(Basic_Salary,Department,"digital marketing")</f>
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <v>150814</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="E16" s="36">
         <v>26246</v>
       </c>
       <c r="F16" s="3" t="s">
@@ -1782,25 +1843,28 @@
       <c r="I16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="37">
         <v>50000</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+      <c r="N16" s="1">
+        <f>_xlfn.MINIFS(Basic_Salary,Region,"South")</f>
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <v>150937</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="E17" s="36">
         <v>24700</v>
       </c>
       <c r="F17" s="3" t="s">
@@ -1815,21 +1879,21 @@
       <c r="I17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="37">
         <v>37000</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <v>150888</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="E18" s="36">
         <v>29221</v>
       </c>
       <c r="F18" s="3" t="s">
@@ -1844,21 +1908,21 @@
       <c r="I18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="37">
         <v>43000</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <v>150865</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E19" s="4">
+        <v>164</v>
+      </c>
+      <c r="E19" s="36">
         <v>31279</v>
       </c>
       <c r="F19" s="3" t="s">
@@ -1873,21 +1937,21 @@
       <c r="I19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="37">
         <v>90000</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <v>150858</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="E20" s="36">
         <v>34846</v>
       </c>
       <c r="F20" s="3" t="s">
@@ -1902,25 +1966,25 @@
       <c r="I20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="37">
         <v>34000</v>
       </c>
-      <c r="M20" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="N20" s="38"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M20" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="N20" s="45"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <v>150930</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="4">
+      <c r="E21" s="36">
         <v>37027</v>
       </c>
       <c r="F21" s="3" t="s">
@@ -1935,11 +1999,11 @@
       <c r="I21" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="37">
         <v>82000</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>36</v>
@@ -1954,17 +2018,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <v>150894</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="4">
+      <c r="E22" s="36">
         <v>37124</v>
       </c>
       <c r="F22" s="3" t="s">
@@ -1979,28 +2043,40 @@
       <c r="I22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="37">
         <v>67000</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N22" s="1">
+        <f t="shared" ref="N22:N32" si="0">SUMIFS(Basic_Salary,Department,M22,Region,"north")</f>
+        <v>48000</v>
+      </c>
+      <c r="O22" s="1">
+        <f t="shared" ref="O22:O32" si="1">SUMIFS(Basic_Salary,Department,M22,Region,"South")</f>
+        <v>62000</v>
+      </c>
+      <c r="P22" s="1">
+        <f t="shared" ref="P22:P32" si="2">SUMIFS(Basic_Salary,Department,M22,Region,"east")</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <f t="shared" ref="Q22:Q32" si="3">SUMIFS(Basic_Salary,Department,M22,Region,"mid west")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <v>150947</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E23" s="4">
+      <c r="E23" s="36">
         <v>33449</v>
       </c>
       <c r="F23" s="3" t="s">
@@ -2015,28 +2091,40 @@
       <c r="I23" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="37">
         <v>85000</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N23" s="1">
+        <f t="shared" si="0"/>
+        <v>183000</v>
+      </c>
+      <c r="O23" s="1">
+        <f t="shared" si="1"/>
+        <v>82000</v>
+      </c>
+      <c r="P23" s="1">
+        <f t="shared" si="2"/>
+        <v>92000</v>
+      </c>
+      <c r="Q23" s="1">
+        <f t="shared" si="3"/>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <v>150905</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E24" s="4">
+      <c r="E24" s="36">
         <v>30819</v>
       </c>
       <c r="F24" s="3" t="s">
@@ -2051,28 +2139,40 @@
       <c r="I24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="37">
         <v>62000</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N24" s="1">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
+      <c r="O24" s="1">
+        <f t="shared" si="1"/>
+        <v>154000</v>
+      </c>
+      <c r="P24" s="1">
+        <f t="shared" si="2"/>
+        <v>95000</v>
+      </c>
+      <c r="Q24" s="1">
+        <f t="shared" si="3"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <v>150995</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="E25" s="36">
         <v>35330</v>
       </c>
       <c r="F25" s="3" t="s">
@@ -2087,28 +2187,40 @@
       <c r="I25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="37">
         <v>15000</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N25" s="1">
+        <f t="shared" si="0"/>
+        <v>22000</v>
+      </c>
+      <c r="O25" s="1">
+        <f t="shared" si="1"/>
+        <v>58000</v>
+      </c>
+      <c r="P25" s="1">
+        <f t="shared" si="2"/>
+        <v>27000</v>
+      </c>
+      <c r="Q25" s="1">
+        <f t="shared" si="3"/>
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <v>150912</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E26" s="4">
+      <c r="E26" s="36">
         <v>37629</v>
       </c>
       <c r="F26" s="3" t="s">
@@ -2123,28 +2235,40 @@
       <c r="I26" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="37">
         <v>81000</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N26" s="1">
+        <f t="shared" si="0"/>
+        <v>91000</v>
+      </c>
+      <c r="O26" s="1">
+        <f t="shared" si="1"/>
+        <v>87000</v>
+      </c>
+      <c r="P26" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="3">
         <v>150921</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E27" s="4">
+      <c r="E27" s="36">
         <v>38092</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -2159,28 +2283,40 @@
       <c r="I27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="37">
         <v>19000</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N27" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <f t="shared" si="1"/>
+        <v>37000</v>
+      </c>
+      <c r="P27" s="1">
+        <f t="shared" si="2"/>
+        <v>43000</v>
+      </c>
+      <c r="Q27" s="1">
+        <f t="shared" si="3"/>
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
         <v>150851</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E28" s="4">
+      <c r="E28" s="36">
         <v>29368</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -2195,28 +2331,40 @@
       <c r="I28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="37">
         <v>75000</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N28" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <f t="shared" si="2"/>
+        <v>90000</v>
+      </c>
+      <c r="Q28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="3">
         <v>150867</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E29" s="4">
+      <c r="E29" s="36">
         <v>29028</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -2231,28 +2379,40 @@
       <c r="I29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="37">
         <v>49000</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N29" s="1">
+        <f t="shared" si="0"/>
+        <v>26000</v>
+      </c>
+      <c r="O29" s="1">
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="P29" s="1">
+        <f t="shared" si="2"/>
+        <v>81000</v>
+      </c>
+      <c r="Q29" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
         <v>150899</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E30" s="4">
+      <c r="E30" s="36">
         <v>37400</v>
       </c>
       <c r="F30" s="3" t="s">
@@ -2267,28 +2427,40 @@
       <c r="I30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="37">
         <v>50000</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N30" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <f t="shared" si="1"/>
+        <v>146000</v>
+      </c>
+      <c r="P30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31" s="3">
         <v>150975</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E31" s="4">
+      <c r="E31" s="36">
         <v>31478</v>
       </c>
       <c r="F31" s="3" t="s">
@@ -2303,28 +2475,40 @@
       <c r="I31" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="37">
         <v>83000</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-    </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="N31" s="1">
+        <f t="shared" si="0"/>
+        <v>85000</v>
+      </c>
+      <c r="O31" s="1">
+        <f t="shared" si="1"/>
+        <v>19000</v>
+      </c>
+      <c r="P31" s="1">
+        <f t="shared" si="2"/>
+        <v>49000</v>
+      </c>
+      <c r="Q31" s="1">
+        <f t="shared" si="3"/>
+        <v>83000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" s="3">
         <v>150901</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E32" s="4">
+      <c r="E32" s="36">
         <v>32946</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -2339,28 +2523,40 @@
       <c r="I32" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="37">
         <v>53000</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="N32" s="1">
+        <f t="shared" si="0"/>
+        <v>52000</v>
+      </c>
+      <c r="O32" s="1">
+        <f t="shared" si="1"/>
+        <v>110000</v>
+      </c>
+      <c r="P32" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="3">
         <v>150968</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E33" s="4">
+      <c r="E33" s="36">
         <v>37208</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -2375,21 +2571,21 @@
       <c r="I33" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="37">
         <v>65000</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="3">
         <v>150773</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E34" s="4">
+      <c r="E34" s="36">
         <v>26860</v>
       </c>
       <c r="F34" s="3" t="s">
@@ -2404,21 +2600,21 @@
       <c r="I34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="37">
         <v>85000</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="3">
         <v>150840</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E35" s="4">
+        <v>198</v>
+      </c>
+      <c r="E35" s="36">
         <v>23136</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -2433,21 +2629,21 @@
       <c r="I35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="37">
         <v>20000</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="3">
         <v>150850</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E36" s="4">
+        <v>199</v>
+      </c>
+      <c r="E36" s="36">
         <v>32027</v>
       </c>
       <c r="F36" s="3" t="s">
@@ -2462,21 +2658,21 @@
       <c r="I36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="37">
         <v>47000</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="3">
         <v>150962</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E37" s="4">
+      <c r="E37" s="36">
         <v>37773</v>
       </c>
       <c r="F37" s="3" t="s">
@@ -2491,21 +2687,21 @@
       <c r="I37" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="37">
         <v>87000</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="3">
         <v>150954</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E38" s="4">
+        <v>201</v>
+      </c>
+      <c r="E38" s="36">
         <v>35495</v>
       </c>
       <c r="F38" s="3" t="s">
@@ -2520,21 +2716,21 @@
       <c r="I38" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="37">
         <v>57000</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="3">
         <v>150874</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E39" s="4">
+        <v>201</v>
+      </c>
+      <c r="E39" s="36">
         <v>37890</v>
       </c>
       <c r="F39" s="3" t="s">
@@ -2549,21 +2745,21 @@
       <c r="I39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="37">
         <v>27000</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="3">
         <v>150798</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E40" s="4">
+        <v>201</v>
+      </c>
+      <c r="E40" s="36">
         <v>28276</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -2578,21 +2774,21 @@
       <c r="I40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="37">
         <v>81000</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="3">
         <v>150830</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E41" s="4">
+      <c r="E41" s="36">
         <v>29037</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -2607,21 +2803,21 @@
       <c r="I41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="37">
         <v>52000</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="3">
         <v>150929</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E42" s="4">
+      <c r="E42" s="36">
         <v>26739</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -2636,21 +2832,21 @@
       <c r="I42" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="37">
         <v>58000</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="3">
         <v>150982</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E43" s="4">
+      <c r="E43" s="36">
         <v>35574</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -2665,21 +2861,21 @@
       <c r="I43" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="37">
         <v>47000</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="3">
         <v>150821</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E44" s="4">
+      <c r="E44" s="36">
         <v>29966</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -2694,7 +2890,7 @@
       <c r="I44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="37">
         <v>26000</v>
       </c>
     </row>
@@ -2710,152 +2906,155 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B1" s="35"/>
-      <c r="C1" s="36" t="s">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="34">
+        <v>1</v>
+      </c>
+      <c r="C2" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="35">
-        <v>1</v>
-      </c>
-      <c r="C2" s="35" t="s">
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="34">
+        <v>2</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="35">
-        <v>2</v>
-      </c>
-      <c r="C3" s="35" t="s">
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="34">
+        <v>3</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="35">
-        <v>3</v>
-      </c>
-      <c r="C4" s="35" t="s">
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="34">
+        <v>4</v>
+      </c>
+      <c r="C5" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="35">
-        <v>4</v>
-      </c>
-      <c r="C5" s="35" t="s">
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="34">
+        <v>5</v>
+      </c>
+      <c r="C6" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="35">
-        <v>5</v>
-      </c>
-      <c r="C6" s="35" t="s">
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="34">
+        <v>6</v>
+      </c>
+      <c r="C7" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="35">
-        <v>6</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-    </row>
-    <row r="10" spans="1:14" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+    </row>
+    <row r="10" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>74</v>
@@ -2875,31 +3074,34 @@
       <c r="I10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="29">
         <v>1</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="29">
         <v>2</v>
       </c>
-      <c r="L10" s="30">
-        <v>3</v>
-      </c>
-      <c r="M10" s="30">
+      <c r="L10" s="29">
+        <v>3</v>
+      </c>
+      <c r="M10" s="29">
         <v>4</v>
       </c>
-      <c r="N10" s="30">
+      <c r="N10" s="29">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" s="31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>150773</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="D11" s="4">
         <v>26860</v>
@@ -2919,21 +3121,37 @@
       <c r="I11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J11" s="31" t="str">
+        <f t="shared" ref="J11:J48" si="0">IF(AND(Gender="Female",Basic_Salary&lt;50000),"Eligible for Gift","Not Eligible for Gift")</f>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K11" s="31">
+        <f t="shared" ref="K11:K48" si="1">IF(AND(Basic_Salary&lt;30000,Department="CCD"),9000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31">
+        <f t="shared" ref="M11:M48" si="2">IF(AND(Department="sales",Basic_Salary&lt;45000),25000,IF(AND(Department="marketing",Basic_Salary&lt;45000),25000,10000))</f>
+        <v>10000</v>
+      </c>
+      <c r="N11" s="31">
+        <f t="shared" ref="N11:N48" si="3">IF(OR(Department="director",Department="CEO"),"",1500)</f>
+        <v>1500</v>
+      </c>
+      <c r="O11" s="31">
+        <f t="shared" ref="O11:O48" si="4">_xlfn.IFS(Region="north",5000,Region="south",4000,Region="east",4200,Region="mid west",3800)</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>150777</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="D12" s="4">
         <v>21123</v>
@@ -2953,21 +3171,37 @@
       <c r="I12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J12" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K12" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31">
+        <f t="shared" si="2"/>
+        <v>25000</v>
+      </c>
+      <c r="N12" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O12" s="31">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>150784</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="D13" s="4">
         <v>28365</v>
@@ -2987,21 +3221,37 @@
       <c r="I13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J13" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible for Gift</v>
+      </c>
+      <c r="K13" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N13" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O13" s="31">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>150791</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="D14" s="4">
         <v>23346</v>
@@ -3021,21 +3271,37 @@
       <c r="I14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J14" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K14" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N14" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O14" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>150798</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D15" s="4">
         <v>28276</v>
@@ -3055,21 +3321,37 @@
       <c r="I15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J15" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K15" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N15" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O15" s="31">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>150805</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D16" s="4">
         <v>26172</v>
@@ -3089,21 +3371,37 @@
       <c r="I16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J16" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K16" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N16" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="O16" s="31">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>150814</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="D17" s="4">
         <v>26246</v>
@@ -3123,21 +3421,37 @@
       <c r="I17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J17" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K17" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N17" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O17" s="31">
+        <f t="shared" si="4"/>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>150821</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="D18" s="4">
         <v>29966</v>
@@ -3157,21 +3471,37 @@
       <c r="I18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J18" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K18" s="31">
+        <f t="shared" si="1"/>
+        <v>9000</v>
+      </c>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N18" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O18" s="31">
+        <f t="shared" si="4"/>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>150830</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="D19" s="4">
         <v>29037</v>
@@ -3191,21 +3521,37 @@
       <c r="I19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J19" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K19" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N19" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O19" s="31">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>150834</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="D20" s="4">
         <v>31199</v>
@@ -3225,21 +3571,37 @@
       <c r="I20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J20" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible for Gift</v>
+      </c>
+      <c r="K20" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N20" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O20" s="31">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>150840</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D21" s="4">
         <v>23136</v>
@@ -3259,21 +3621,37 @@
       <c r="I21" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J21" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible for Gift</v>
+      </c>
+      <c r="K21" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N21" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O21" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>150850</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D22" s="4">
         <v>32027</v>
@@ -3293,21 +3671,37 @@
       <c r="I22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J22" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K22" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N22" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O22" s="31">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>150851</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="D23" s="4">
         <v>29368</v>
@@ -3327,21 +3721,37 @@
       <c r="I23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J23" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K23" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N23" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O23" s="31">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>150858</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="D24" s="4">
         <v>34846</v>
@@ -3361,21 +3771,37 @@
       <c r="I24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J24" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K24" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N24" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O24" s="31">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>150865</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D25" s="4">
         <v>31279</v>
@@ -3395,21 +3821,37 @@
       <c r="I25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J25" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K25" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N25" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="O25" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>150867</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="D26" s="4">
         <v>29028</v>
@@ -3429,21 +3871,37 @@
       <c r="I26" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J26" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible for Gift</v>
+      </c>
+      <c r="K26" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N26" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O26" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>150874</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D27" s="4">
         <v>37890</v>
@@ -3463,21 +3921,37 @@
       <c r="I27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J27" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible for Gift</v>
+      </c>
+      <c r="K27" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31">
+        <f t="shared" si="2"/>
+        <v>25000</v>
+      </c>
+      <c r="N27" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O27" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>150881</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="D28" s="4">
         <v>30337</v>
@@ -3497,21 +3971,37 @@
       <c r="I28" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J28" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K28" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N28" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O28" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>150888</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="D29" s="4">
         <v>29221</v>
@@ -3531,21 +4021,37 @@
       <c r="I29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J29" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K29" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N29" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O29" s="31">
+        <f t="shared" si="4"/>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>150894</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D30" s="4">
         <v>37124</v>
@@ -3565,21 +4071,37 @@
       <c r="I30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J30" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K30" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N30" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O30" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>150899</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D31" s="4">
         <v>37400</v>
@@ -3599,21 +4121,37 @@
       <c r="I31" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J31" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K31" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N31" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O31" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>150901</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="D32" s="4">
         <v>32946</v>
@@ -3633,21 +4171,37 @@
       <c r="I32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J32" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K32" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N32" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O32" s="31">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>150905</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="D33" s="4">
         <v>30819</v>
@@ -3667,21 +4221,37 @@
       <c r="I33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J33" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K33" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N33" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O33" s="31">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>150912</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="D34" s="4">
         <v>37629</v>
@@ -3701,21 +4271,37 @@
       <c r="I34" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J34" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K34" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="31"/>
+      <c r="M34" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N34" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O34" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>150921</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="D35" s="4">
         <v>38092</v>
@@ -3735,21 +4321,37 @@
       <c r="I35" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J35" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K35" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="31"/>
+      <c r="M35" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N35" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O35" s="31">
+        <f t="shared" si="4"/>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>150929</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="D36" s="4">
         <v>26739</v>
@@ -3769,21 +4371,37 @@
       <c r="I36" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J36" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K36" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="31"/>
+      <c r="M36" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N36" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O36" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>150930</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="D37" s="4">
         <v>37027</v>
@@ -3803,21 +4421,37 @@
       <c r="I37" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
-      <c r="N37" s="32"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J37" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K37" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N37" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O37" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>150937</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="D38" s="4">
         <v>24700</v>
@@ -3837,21 +4471,37 @@
       <c r="I38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
-      <c r="M38" s="32"/>
-      <c r="N38" s="32"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J38" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K38" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="31"/>
+      <c r="M38" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N38" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O38" s="31">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>150940</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D39" s="4">
         <v>26906</v>
@@ -3871,21 +4521,37 @@
       <c r="I39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J39" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K39" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="31"/>
+      <c r="M39" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N39" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O39" s="31">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>150947</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D40" s="4">
         <v>33449</v>
@@ -3905,21 +4571,37 @@
       <c r="I40" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
-      <c r="N40" s="32"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J40" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K40" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N40" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O40" s="31">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>150954</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D41" s="4">
         <v>35495</v>
@@ -3939,21 +4621,37 @@
       <c r="I41" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
-      <c r="N41" s="32"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J41" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K41" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N41" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O41" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>150962</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="D42" s="4">
         <v>37773</v>
@@ -3973,21 +4671,37 @@
       <c r="I42" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
-      <c r="N42" s="32"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J42" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K42" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N42" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="O42" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>150968</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="D43" s="4">
         <v>37208</v>
@@ -4007,21 +4721,37 @@
       <c r="I43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
-      <c r="N43" s="32"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J43" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K43" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N43" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O43" s="31">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>150975</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="D44" s="4">
         <v>31478</v>
@@ -4041,21 +4771,37 @@
       <c r="I44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="32"/>
-      <c r="K44" s="32"/>
-      <c r="L44" s="32"/>
-      <c r="M44" s="32"/>
-      <c r="N44" s="32"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J44" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K44" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N44" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O44" s="31">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>150982</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D45" s="4">
         <v>35574</v>
@@ -4075,21 +4821,37 @@
       <c r="I45" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="32"/>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
-      <c r="M45" s="32"/>
-      <c r="N45" s="32"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J45" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K45" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L45" s="31"/>
+      <c r="M45" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N45" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O45" s="31">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>150989</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D46" s="4">
         <v>33113</v>
@@ -4109,21 +4871,37 @@
       <c r="I46" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J46" s="32"/>
-      <c r="K46" s="32"/>
-      <c r="L46" s="32"/>
-      <c r="M46" s="32"/>
-      <c r="N46" s="32"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J46" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K46" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N46" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O46" s="31">
+        <f t="shared" si="4"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>150990</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D47" s="4">
         <v>36400</v>
@@ -4143,21 +4921,37 @@
       <c r="I47" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
-      <c r="M47" s="32"/>
-      <c r="N47" s="32"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J47" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K47" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N47" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O47" s="31">
+        <f t="shared" si="4"/>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>150995</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="D48" s="4">
         <v>35330</v>
@@ -4177,14 +4971,30 @@
       <c r="I48" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J48" s="32"/>
-      <c r="K48" s="32"/>
-      <c r="L48" s="32"/>
-      <c r="M48" s="32"/>
-      <c r="N48" s="32"/>
-    </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G49" s="33"/>
+      <c r="J48" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible for Gift</v>
+      </c>
+      <c r="K48" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="31"/>
+      <c r="M48" s="31">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N48" s="31">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="O48" s="31">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G49" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4194,21 +5004,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="C2:M44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="19.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.21875" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" customWidth="1"/>
-    <col min="11" max="11" width="8.21875" customWidth="1"/>
-    <col min="12" max="12" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -4221,23 +5030,23 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C3" s="6">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C6" s="5" t="s">
         <v>65</v>
       </c>
@@ -4272,15 +5081,19 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C7" s="39">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>146</v>
+      </c>
       <c r="G7" s="4">
         <v>26123</v>
       </c>
@@ -4299,17 +5112,24 @@
       <c r="L7" s="1">
         <v>22000</v>
       </c>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M7" s="8" t="str">
+        <f>UPPER(_xlfn.CONCAT(LEFT(E7,2),LEFT(J7,2),LEFT(K7,1),C7))</f>
+        <v>MEMAN1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C8" s="3">
         <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="E8" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>198</v>
+      </c>
       <c r="G8" s="4">
         <v>28136</v>
       </c>
@@ -4328,17 +5148,24 @@
       <c r="L8" s="1">
         <v>20000</v>
       </c>
-      <c r="M8" s="8"/>
-    </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M8" s="8" t="str">
+        <f t="shared" ref="M8:M44" si="0">UPPER(_xlfn.CONCAT(LEFT(E8,2),LEFT(J8,2),LEFT(K8,1),C8))</f>
+        <v>PIINE2</v>
+      </c>
+    </row>
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C9" s="3">
         <v>3</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="G9" s="4">
         <v>28346</v>
       </c>
@@ -4357,17 +5184,24 @@
       <c r="L9" s="1">
         <v>67000</v>
       </c>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RADIN3</v>
+      </c>
+    </row>
+    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C10" s="3">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="G10" s="4">
         <v>29700</v>
       </c>
@@ -4386,17 +5220,24 @@
       <c r="L10" s="1">
         <v>37000</v>
       </c>
-      <c r="M10" s="8"/>
-    </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M10" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>DHLES4</v>
+      </c>
+    </row>
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C11" s="3">
         <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>148</v>
+      </c>
       <c r="G11" s="4">
         <v>31172</v>
       </c>
@@ -4415,17 +5256,24 @@
       <c r="L11" s="1">
         <v>91000</v>
       </c>
-      <c r="M11" s="8"/>
-    </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M11" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RADIN5</v>
+      </c>
+    </row>
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C12" s="3">
         <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>159</v>
+      </c>
       <c r="G12" s="4">
         <v>31246</v>
       </c>
@@ -4444,17 +5292,24 @@
       <c r="L12" s="1">
         <v>50000</v>
       </c>
-      <c r="M12" s="8"/>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M12" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>HEINN6</v>
+      </c>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="3">
         <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>208</v>
+      </c>
       <c r="G13" s="4">
         <v>31739</v>
       </c>
@@ -4473,17 +5328,24 @@
       <c r="L13" s="1">
         <v>58000</v>
       </c>
-      <c r="M13" s="8"/>
-    </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M13" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>BOMAS7</v>
+      </c>
+    </row>
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C14" s="3">
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="E14" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>197</v>
+      </c>
       <c r="G14" s="4">
         <v>31860</v>
       </c>
@@ -4502,17 +5364,24 @@
       <c r="L14" s="1">
         <v>85000</v>
       </c>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>STFIN8</v>
+      </c>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C15" s="3">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="E15" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>143</v>
+      </c>
       <c r="G15" s="4">
         <v>31906</v>
       </c>
@@ -4531,17 +5400,24 @@
       <c r="L15" s="1">
         <v>87000</v>
       </c>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M15" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RAINS9</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C16" s="3">
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="E16" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="G16" s="4">
         <v>33276</v>
       </c>
@@ -4560,17 +5436,24 @@
       <c r="L16" s="1">
         <v>81000</v>
       </c>
-      <c r="M16" s="8"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M16" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>TUDIN10</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C17" s="3">
         <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="E17" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="G17" s="4">
         <v>33365</v>
       </c>
@@ -4589,17 +5472,24 @@
       <c r="L17" s="1">
         <v>35000</v>
       </c>
-      <c r="M17" s="8"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M17" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>SADIN11</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C18" s="3">
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="E18" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="G18" s="4">
         <v>34028</v>
       </c>
@@ -4618,17 +5508,24 @@
       <c r="L18" s="1">
         <v>49000</v>
       </c>
-      <c r="M18" s="8"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M18" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>BOFIE12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C19" s="3">
         <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="E19" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>206</v>
+      </c>
       <c r="G19" s="4">
         <v>34037</v>
       </c>
@@ -4647,17 +5544,24 @@
       <c r="L19" s="1">
         <v>52000</v>
       </c>
-      <c r="M19" s="8"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M19" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RASAN13</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C20" s="3">
         <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="E20" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="G20" s="4">
         <v>34221</v>
       </c>
@@ -4676,17 +5580,24 @@
       <c r="L20" s="1">
         <v>43000</v>
       </c>
-      <c r="M20" s="8"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M20" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>GULEE14</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C21" s="3">
         <v>15</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="E21" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>185</v>
+      </c>
       <c r="G21" s="4">
         <v>34368</v>
       </c>
@@ -4705,17 +5616,24 @@
       <c r="L21" s="1">
         <v>75000</v>
       </c>
-      <c r="M21" s="8"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M21" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>SUINE15</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C22" s="3">
         <v>16</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="E22" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>212</v>
+      </c>
       <c r="G22" s="4">
         <v>34966</v>
       </c>
@@ -4734,17 +5652,24 @@
       <c r="L22" s="1">
         <v>26000</v>
       </c>
-      <c r="M22" s="8"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M22" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>YACCN16</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C23" s="3">
         <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="E23" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>156</v>
+      </c>
       <c r="G23" s="4">
         <v>35337</v>
       </c>
@@ -4763,17 +5688,24 @@
       <c r="L23" s="1">
         <v>92000</v>
       </c>
-      <c r="M23" s="8"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M23" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>DIDIE17</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C24" s="3">
         <v>18</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="E24" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>177</v>
+      </c>
       <c r="G24" s="4">
         <v>35819</v>
       </c>
@@ -4792,17 +5724,24 @@
       <c r="L24" s="1">
         <v>62000</v>
       </c>
-      <c r="M24" s="8"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M24" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>YOFLS18</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C25" s="3">
         <v>19</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="E25" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>135</v>
+      </c>
       <c r="G25" s="4">
         <v>36199</v>
       </c>
@@ -4821,17 +5760,24 @@
       <c r="L25" s="1">
         <v>48000</v>
       </c>
-      <c r="M25" s="8"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M25" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RAFLN19</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C26" s="3">
         <v>20</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="E26" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="G26" s="4">
         <v>36279</v>
       </c>
@@ -4850,17 +5796,24 @@
       <c r="L26" s="1">
         <v>90000</v>
       </c>
-      <c r="M26" s="8"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M26" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RUCEE20</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C27" s="3">
         <v>21</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
+      <c r="E27" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>191</v>
+      </c>
       <c r="G27" s="4">
         <v>36478</v>
       </c>
@@ -4879,17 +5832,24 @@
       <c r="L27" s="1">
         <v>83000</v>
       </c>
-      <c r="M27" s="8"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M27" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>SIFIM21</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C28" s="3">
         <v>22</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
+      <c r="E28" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>199</v>
+      </c>
       <c r="G28" s="4">
         <v>37027</v>
       </c>
@@ -4908,17 +5868,24 @@
       <c r="L28" s="1">
         <v>47000</v>
       </c>
-      <c r="M28" s="8"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M28" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>DHCCE22</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C29" s="3">
         <v>23</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="E29" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>193</v>
+      </c>
       <c r="G29" s="4">
         <v>37946</v>
       </c>
@@ -4937,17 +5904,24 @@
       <c r="L29" s="1">
         <v>53000</v>
       </c>
-      <c r="M29" s="8"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M29" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>ASSAS23</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C30" s="3">
         <v>24</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="E30" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>151</v>
+      </c>
       <c r="G30" s="4">
         <v>38113</v>
       </c>
@@ -4966,17 +5940,24 @@
       <c r="L30" s="1">
         <v>45000</v>
       </c>
-      <c r="M30" s="8"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M30" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>VIDIM24</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C31" s="3">
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="E31" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>175</v>
+      </c>
       <c r="G31" s="4">
         <v>38449</v>
       </c>
@@ -4995,17 +5976,24 @@
       <c r="L31" s="1">
         <v>85000</v>
       </c>
-      <c r="M31" s="8"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M31" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RACCS25</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C32" s="3">
         <v>26</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
+      <c r="E32" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="G32" s="4">
         <v>39846</v>
       </c>
@@ -5024,17 +6012,24 @@
       <c r="L32" s="1">
         <v>34000</v>
       </c>
-      <c r="M32" s="8"/>
-    </row>
-    <row r="33" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M32" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>JACCE26</v>
+      </c>
+    </row>
+    <row r="33" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C33" s="3">
         <v>27</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="E33" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>179</v>
+      </c>
       <c r="G33" s="4">
         <v>40330</v>
       </c>
@@ -5053,17 +6048,24 @@
       <c r="L33" s="1">
         <v>15000</v>
       </c>
-      <c r="M33" s="8"/>
-    </row>
-    <row r="34" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M33" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>SAINM27</v>
+      </c>
+    </row>
+    <row r="34" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C34" s="3">
         <v>28</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="E34" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="G34" s="4">
         <v>40495</v>
       </c>
@@ -5082,17 +6084,24 @@
       <c r="L34" s="1">
         <v>57000</v>
       </c>
-      <c r="M34" s="8"/>
-    </row>
-    <row r="35" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M34" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>KASAS28</v>
+      </c>
+    </row>
+    <row r="35" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C35" s="3">
         <v>29</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
+      <c r="E35" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>210</v>
+      </c>
       <c r="G35" s="4">
         <v>40574</v>
       </c>
@@ -5111,17 +6120,24 @@
       <c r="L35" s="1">
         <v>47000</v>
       </c>
-      <c r="M35" s="8"/>
-    </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M35" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>JIMAM29</v>
+      </c>
+    </row>
+    <row r="36" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C36" s="3">
         <v>30</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
+      <c r="E36" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>151</v>
+      </c>
       <c r="G36" s="4">
         <v>41400</v>
       </c>
@@ -5140,17 +6156,24 @@
       <c r="L36" s="1">
         <v>77000</v>
       </c>
-      <c r="M36" s="8"/>
-    </row>
-    <row r="37" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M36" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>DALEM30</v>
+      </c>
+    </row>
+    <row r="37" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C37" s="3">
         <v>31</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
+      <c r="E37" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="G37" s="4">
         <v>42027</v>
       </c>
@@ -5169,17 +6192,24 @@
       <c r="L37" s="1">
         <v>82000</v>
       </c>
-      <c r="M37" s="8"/>
-    </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M37" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>PIDIS31</v>
+      </c>
+    </row>
+    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C38" s="3">
         <v>32</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="E38" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="G38" s="4">
         <v>42124</v>
       </c>
@@ -5198,17 +6228,24 @@
       <c r="L38" s="1">
         <v>67000</v>
       </c>
-      <c r="M38" s="8"/>
-    </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M38" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>DINS32</v>
+      </c>
+    </row>
+    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C39" s="3">
         <v>33</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="E39" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>195</v>
+      </c>
       <c r="G39" s="4">
         <v>42208</v>
       </c>
@@ -5227,17 +6264,24 @@
       <c r="L39" s="1">
         <v>65000</v>
       </c>
-      <c r="M39" s="8"/>
-    </row>
-    <row r="40" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M39" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>PROPS33</v>
+      </c>
+    </row>
+    <row r="40" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C40" s="3">
         <v>34</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
+      <c r="E40" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>189</v>
+      </c>
       <c r="G40" s="4">
         <v>42400</v>
       </c>
@@ -5256,17 +6300,24 @@
       <c r="L40" s="1">
         <v>50000</v>
       </c>
-      <c r="M40" s="8"/>
-    </row>
-    <row r="41" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M40" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>SHCCS34</v>
+      </c>
+    </row>
+    <row r="41" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C41" s="3">
         <v>35</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
+      <c r="E41" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="G41" s="4">
         <v>42629</v>
       </c>
@@ -5285,17 +6336,24 @@
       <c r="L41" s="1">
         <v>81000</v>
       </c>
-      <c r="M41" s="8"/>
-    </row>
-    <row r="42" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M41" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NIOPS35</v>
+      </c>
+    </row>
+    <row r="42" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C42" s="3">
         <v>36</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
+      <c r="E42" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="G42" s="4">
         <v>42773</v>
       </c>
@@ -5314,17 +6372,24 @@
       <c r="L42" s="1">
         <v>87000</v>
       </c>
-      <c r="M42" s="8"/>
-    </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M42" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>SHDIS36</v>
+      </c>
+    </row>
+    <row r="43" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C43" s="3">
         <v>37</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="E43" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="G43" s="4">
         <v>42890</v>
       </c>
@@ -5343,17 +6408,24 @@
       <c r="L43" s="1">
         <v>27000</v>
       </c>
-      <c r="M43" s="8"/>
-    </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M43" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>VEMAE37</v>
+      </c>
+    </row>
+    <row r="44" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C44" s="3">
         <v>38</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
+      <c r="E44" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>183</v>
+      </c>
       <c r="G44" s="4">
         <v>43092</v>
       </c>
@@ -5372,7 +6444,10 @@
       <c r="L44" s="1">
         <v>19000</v>
       </c>
-      <c r="M44" s="8"/>
+      <c r="M44" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>PRFIS38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5382,37 +6457,50 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B3:I33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="10"/>
+      <c r="C3" s="40">
+        <f ca="1">TODAY()</f>
+        <v>46241</v>
+      </c>
       <c r="F3" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="10"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G3" s="40">
+        <f ca="1">TODAY()-14</f>
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="41">
+        <f ca="1">NOW()</f>
+        <v>46241.623535995372</v>
+      </c>
       <c r="F4" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="10"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G4" s="41">
+        <f ca="1">NOW()-14</f>
+        <v>46227.623535995372</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>73</v>
       </c>
@@ -5438,180 +6526,396 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C7" s="4">
         <v>36478</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D7" s="10">
+        <f>DAY(C7)</f>
+        <v>14</v>
+      </c>
+      <c r="E7" s="10">
+        <f>MONTH(C7)</f>
+        <v>11</v>
+      </c>
+      <c r="F7" s="10" t="str">
+        <f>TEXT(C7,"mmm")</f>
+        <v>Nov</v>
+      </c>
+      <c r="G7" s="10">
+        <f>YEAR(C7)</f>
+        <v>1999</v>
+      </c>
+      <c r="H7" s="40" t="str">
+        <f ca="1">TEXT(TODAY()-C7,"yy")</f>
+        <v>26</v>
+      </c>
+      <c r="I7" s="43" t="str">
+        <f ca="1">DATEDIF(C7,$C$3,"Y")&amp;" Years, "&amp;DATEDIF(C7,$C$3,"YM")&amp;" Months, "&amp;DATEDIF(C7,$C$3,"MD")&amp;" Days"</f>
+        <v>26 Years, 8 Months, 24 Days</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="4">
         <v>37027</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D8" s="10">
+        <f t="shared" ref="D8:D18" si="0">DAY(C8)</f>
+        <v>16</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" ref="E8:E18" si="1">MONTH(C8)</f>
+        <v>5</v>
+      </c>
+      <c r="F8" s="10" t="str">
+        <f t="shared" ref="F8:F18" si="2">TEXT(C8,"mmm")</f>
+        <v>May</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" ref="G8:G18" si="3">YEAR(C8)</f>
+        <v>2001</v>
+      </c>
+      <c r="H8" s="40" t="str">
+        <f t="shared" ref="H8:H18" ca="1" si="4">TEXT(TODAY()-C8,"yy")</f>
+        <v>25</v>
+      </c>
+      <c r="I8" s="43" t="str">
+        <f t="shared" ref="I8:I18" ca="1" si="5">DATEDIF(C8,$C$3,"Y")&amp;" Years, "&amp;DATEDIF(C8,$C$3,"YM")&amp;" Months, "&amp;DATEDIF(C8,$C$3,"MD")&amp;" Days"</f>
+        <v>25 Years, 2 Months, 22 Days</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="4">
         <v>37946</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D9" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="F9" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>Nov</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="3"/>
+        <v>2003</v>
+      </c>
+      <c r="H9" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="I9" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>22 Years, 8 Months, 17 Days</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="4">
         <v>38113</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D10" s="10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F10" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>May</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="3"/>
+        <v>2004</v>
+      </c>
+      <c r="H10" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="I10" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>22 Years, 3 Months, 1 Days</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="4">
         <v>38449</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D11" s="10">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F11" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>Apr</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="3"/>
+        <v>2005</v>
+      </c>
+      <c r="H11" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="I11" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>21 Years, 4 Months, 0 Days</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="4">
         <v>39846</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D12" s="10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F12" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="3"/>
+        <v>2009</v>
+      </c>
+      <c r="H12" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="I12" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>17 Years, 6 Months, 5 Days</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="4">
         <v>40330</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D13" s="10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F13" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>Jun</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="3"/>
+        <v>2010</v>
+      </c>
+      <c r="H13" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="I13" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>16 Years, 2 Months, 6 Days</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="4">
         <v>40495</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D14" s="10">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="E14" s="10">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="F14" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>Nov</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="3"/>
+        <v>2010</v>
+      </c>
+      <c r="H14" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="I14" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>15 Years, 8 Months, 25 Days</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="4">
         <v>40574</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D15" s="10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="E15" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F15" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>Jan</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" si="3"/>
+        <v>2011</v>
+      </c>
+      <c r="H15" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="I15" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>15 Years, 6 Months, 7 Days</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="4">
         <v>41400</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D16" s="10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F16" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>May</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="3"/>
+        <v>2013</v>
+      </c>
+      <c r="H16" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="I16" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>13 Years, 3 Months, 1 Days</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="4">
         <v>42027</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D17" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="E17" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F17" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>Jan</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" si="3"/>
+        <v>2015</v>
+      </c>
+      <c r="H17" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="I17" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>11 Years, 6 Months, 15 Days</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="4">
         <v>42124</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D18" s="10">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E18" s="10">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F18" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>Apr</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" si="3"/>
+        <v>2015</v>
+      </c>
+      <c r="H18" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="I18" s="43" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>11 Years, 3 Months, 8 Days</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
         <v>82</v>
       </c>
@@ -5619,76 +6923,85 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="13">
-        <v>20070623</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="15">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" s="42">
+        <f>DATE(LEFT(B25,4),MID(B25,5,2),MID(B25,7,2))</f>
+        <v>39256</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="14">
         <v>20070624</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B27" s="15">
+      <c r="C26" s="42">
+        <f t="shared" ref="C26:C33" si="6">DATE(LEFT(B26,4),MID(B26,5,2),MID(B26,7,2))</f>
+        <v>39257</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="14">
         <v>20070523</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B28" s="15">
+      <c r="C27" s="42">
+        <f t="shared" si="6"/>
+        <v>39225</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="14">
         <v>20061202</v>
       </c>
-      <c r="C28" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="15">
+      <c r="C28" s="42">
+        <f t="shared" si="6"/>
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="14">
         <v>20070112</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="15">
+      <c r="C29" s="42">
+        <f t="shared" si="6"/>
+        <v>39094</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="14">
         <v>20070519</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B31" s="15">
+      <c r="C30" s="42">
+        <f t="shared" si="6"/>
+        <v>39221</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="14">
         <v>20080419</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="15">
+      <c r="C31" s="42">
+        <f t="shared" si="6"/>
+        <v>39557</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="14">
         <v>20071017</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="16">
+      <c r="C32" s="42">
+        <f t="shared" si="6"/>
+        <v>39372</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="15">
         <v>20051220</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>84</v>
+      <c r="C33" s="42">
+        <f t="shared" si="6"/>
+        <v>38706</v>
       </c>
     </row>
   </sheetData>
@@ -5699,780 +7012,780 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.77734375" style="17" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="17" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="17"/>
-    <col min="6" max="6" width="12.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="17"/>
-    <col min="8" max="8" width="43" style="17" customWidth="1"/>
-    <col min="9" max="11" width="8.88671875" style="17"/>
-    <col min="12" max="12" width="12.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.88671875" style="17"/>
-    <col min="15" max="15" width="43.21875" style="17" customWidth="1"/>
-    <col min="16" max="18" width="8.88671875" style="17"/>
-    <col min="19" max="19" width="12.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="256" width="8.88671875" style="17"/>
-    <col min="257" max="257" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="258" max="258" width="11.77734375" style="17" customWidth="1"/>
-    <col min="259" max="259" width="10.33203125" style="17" customWidth="1"/>
-    <col min="260" max="260" width="12.33203125" style="17" customWidth="1"/>
-    <col min="261" max="261" width="8.88671875" style="17"/>
-    <col min="262" max="262" width="10.109375" style="17" customWidth="1"/>
-    <col min="263" max="263" width="8.88671875" style="17"/>
-    <col min="264" max="264" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="265" max="512" width="8.88671875" style="17"/>
-    <col min="513" max="513" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="514" max="514" width="11.77734375" style="17" customWidth="1"/>
-    <col min="515" max="515" width="10.33203125" style="17" customWidth="1"/>
-    <col min="516" max="516" width="12.33203125" style="17" customWidth="1"/>
-    <col min="517" max="517" width="8.88671875" style="17"/>
-    <col min="518" max="518" width="10.109375" style="17" customWidth="1"/>
-    <col min="519" max="519" width="8.88671875" style="17"/>
-    <col min="520" max="520" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="521" max="768" width="8.88671875" style="17"/>
-    <col min="769" max="769" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="770" max="770" width="11.77734375" style="17" customWidth="1"/>
-    <col min="771" max="771" width="10.33203125" style="17" customWidth="1"/>
-    <col min="772" max="772" width="12.33203125" style="17" customWidth="1"/>
-    <col min="773" max="773" width="8.88671875" style="17"/>
-    <col min="774" max="774" width="10.109375" style="17" customWidth="1"/>
-    <col min="775" max="775" width="8.88671875" style="17"/>
-    <col min="776" max="776" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="777" max="1024" width="8.88671875" style="17"/>
-    <col min="1025" max="1025" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="1026" max="1026" width="11.77734375" style="17" customWidth="1"/>
-    <col min="1027" max="1027" width="10.33203125" style="17" customWidth="1"/>
-    <col min="1028" max="1028" width="12.33203125" style="17" customWidth="1"/>
-    <col min="1029" max="1029" width="8.88671875" style="17"/>
-    <col min="1030" max="1030" width="10.109375" style="17" customWidth="1"/>
-    <col min="1031" max="1031" width="8.88671875" style="17"/>
-    <col min="1032" max="1032" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="1033" max="1280" width="8.88671875" style="17"/>
-    <col min="1281" max="1281" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="1282" max="1282" width="11.77734375" style="17" customWidth="1"/>
-    <col min="1283" max="1283" width="10.33203125" style="17" customWidth="1"/>
-    <col min="1284" max="1284" width="12.33203125" style="17" customWidth="1"/>
-    <col min="1285" max="1285" width="8.88671875" style="17"/>
-    <col min="1286" max="1286" width="10.109375" style="17" customWidth="1"/>
-    <col min="1287" max="1287" width="8.88671875" style="17"/>
-    <col min="1288" max="1288" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="1289" max="1536" width="8.88671875" style="17"/>
-    <col min="1537" max="1537" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="1538" max="1538" width="11.77734375" style="17" customWidth="1"/>
-    <col min="1539" max="1539" width="10.33203125" style="17" customWidth="1"/>
-    <col min="1540" max="1540" width="12.33203125" style="17" customWidth="1"/>
-    <col min="1541" max="1541" width="8.88671875" style="17"/>
-    <col min="1542" max="1542" width="10.109375" style="17" customWidth="1"/>
-    <col min="1543" max="1543" width="8.88671875" style="17"/>
-    <col min="1544" max="1544" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="1545" max="1792" width="8.88671875" style="17"/>
-    <col min="1793" max="1793" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="1794" max="1794" width="11.77734375" style="17" customWidth="1"/>
-    <col min="1795" max="1795" width="10.33203125" style="17" customWidth="1"/>
-    <col min="1796" max="1796" width="12.33203125" style="17" customWidth="1"/>
-    <col min="1797" max="1797" width="8.88671875" style="17"/>
-    <col min="1798" max="1798" width="10.109375" style="17" customWidth="1"/>
-    <col min="1799" max="1799" width="8.88671875" style="17"/>
-    <col min="1800" max="1800" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="1801" max="2048" width="8.88671875" style="17"/>
-    <col min="2049" max="2049" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2050" max="2050" width="11.77734375" style="17" customWidth="1"/>
-    <col min="2051" max="2051" width="10.33203125" style="17" customWidth="1"/>
-    <col min="2052" max="2052" width="12.33203125" style="17" customWidth="1"/>
-    <col min="2053" max="2053" width="8.88671875" style="17"/>
-    <col min="2054" max="2054" width="10.109375" style="17" customWidth="1"/>
-    <col min="2055" max="2055" width="8.88671875" style="17"/>
-    <col min="2056" max="2056" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="2057" max="2304" width="8.88671875" style="17"/>
-    <col min="2305" max="2305" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2306" max="2306" width="11.77734375" style="17" customWidth="1"/>
-    <col min="2307" max="2307" width="10.33203125" style="17" customWidth="1"/>
-    <col min="2308" max="2308" width="12.33203125" style="17" customWidth="1"/>
-    <col min="2309" max="2309" width="8.88671875" style="17"/>
-    <col min="2310" max="2310" width="10.109375" style="17" customWidth="1"/>
-    <col min="2311" max="2311" width="8.88671875" style="17"/>
-    <col min="2312" max="2312" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="2313" max="2560" width="8.88671875" style="17"/>
-    <col min="2561" max="2561" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2562" max="2562" width="11.77734375" style="17" customWidth="1"/>
-    <col min="2563" max="2563" width="10.33203125" style="17" customWidth="1"/>
-    <col min="2564" max="2564" width="12.33203125" style="17" customWidth="1"/>
-    <col min="2565" max="2565" width="8.88671875" style="17"/>
-    <col min="2566" max="2566" width="10.109375" style="17" customWidth="1"/>
-    <col min="2567" max="2567" width="8.88671875" style="17"/>
-    <col min="2568" max="2568" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="2569" max="2816" width="8.88671875" style="17"/>
-    <col min="2817" max="2817" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2818" max="2818" width="11.77734375" style="17" customWidth="1"/>
-    <col min="2819" max="2819" width="10.33203125" style="17" customWidth="1"/>
-    <col min="2820" max="2820" width="12.33203125" style="17" customWidth="1"/>
-    <col min="2821" max="2821" width="8.88671875" style="17"/>
-    <col min="2822" max="2822" width="10.109375" style="17" customWidth="1"/>
-    <col min="2823" max="2823" width="8.88671875" style="17"/>
-    <col min="2824" max="2824" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="2825" max="3072" width="8.88671875" style="17"/>
-    <col min="3073" max="3073" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="3074" max="3074" width="11.77734375" style="17" customWidth="1"/>
-    <col min="3075" max="3075" width="10.33203125" style="17" customWidth="1"/>
-    <col min="3076" max="3076" width="12.33203125" style="17" customWidth="1"/>
-    <col min="3077" max="3077" width="8.88671875" style="17"/>
-    <col min="3078" max="3078" width="10.109375" style="17" customWidth="1"/>
-    <col min="3079" max="3079" width="8.88671875" style="17"/>
-    <col min="3080" max="3080" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="3081" max="3328" width="8.88671875" style="17"/>
-    <col min="3329" max="3329" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="3330" max="3330" width="11.77734375" style="17" customWidth="1"/>
-    <col min="3331" max="3331" width="10.33203125" style="17" customWidth="1"/>
-    <col min="3332" max="3332" width="12.33203125" style="17" customWidth="1"/>
-    <col min="3333" max="3333" width="8.88671875" style="17"/>
-    <col min="3334" max="3334" width="10.109375" style="17" customWidth="1"/>
-    <col min="3335" max="3335" width="8.88671875" style="17"/>
-    <col min="3336" max="3336" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="3337" max="3584" width="8.88671875" style="17"/>
-    <col min="3585" max="3585" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="3586" max="3586" width="11.77734375" style="17" customWidth="1"/>
-    <col min="3587" max="3587" width="10.33203125" style="17" customWidth="1"/>
-    <col min="3588" max="3588" width="12.33203125" style="17" customWidth="1"/>
-    <col min="3589" max="3589" width="8.88671875" style="17"/>
-    <col min="3590" max="3590" width="10.109375" style="17" customWidth="1"/>
-    <col min="3591" max="3591" width="8.88671875" style="17"/>
-    <col min="3592" max="3592" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="3593" max="3840" width="8.88671875" style="17"/>
-    <col min="3841" max="3841" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="3842" max="3842" width="11.77734375" style="17" customWidth="1"/>
-    <col min="3843" max="3843" width="10.33203125" style="17" customWidth="1"/>
-    <col min="3844" max="3844" width="12.33203125" style="17" customWidth="1"/>
-    <col min="3845" max="3845" width="8.88671875" style="17"/>
-    <col min="3846" max="3846" width="10.109375" style="17" customWidth="1"/>
-    <col min="3847" max="3847" width="8.88671875" style="17"/>
-    <col min="3848" max="3848" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="3849" max="4096" width="8.88671875" style="17"/>
-    <col min="4097" max="4097" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4098" max="4098" width="11.77734375" style="17" customWidth="1"/>
-    <col min="4099" max="4099" width="10.33203125" style="17" customWidth="1"/>
-    <col min="4100" max="4100" width="12.33203125" style="17" customWidth="1"/>
-    <col min="4101" max="4101" width="8.88671875" style="17"/>
-    <col min="4102" max="4102" width="10.109375" style="17" customWidth="1"/>
-    <col min="4103" max="4103" width="8.88671875" style="17"/>
-    <col min="4104" max="4104" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="4105" max="4352" width="8.88671875" style="17"/>
-    <col min="4353" max="4353" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4354" max="4354" width="11.77734375" style="17" customWidth="1"/>
-    <col min="4355" max="4355" width="10.33203125" style="17" customWidth="1"/>
-    <col min="4356" max="4356" width="12.33203125" style="17" customWidth="1"/>
-    <col min="4357" max="4357" width="8.88671875" style="17"/>
-    <col min="4358" max="4358" width="10.109375" style="17" customWidth="1"/>
-    <col min="4359" max="4359" width="8.88671875" style="17"/>
-    <col min="4360" max="4360" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="4361" max="4608" width="8.88671875" style="17"/>
-    <col min="4609" max="4609" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4610" max="4610" width="11.77734375" style="17" customWidth="1"/>
-    <col min="4611" max="4611" width="10.33203125" style="17" customWidth="1"/>
-    <col min="4612" max="4612" width="12.33203125" style="17" customWidth="1"/>
-    <col min="4613" max="4613" width="8.88671875" style="17"/>
-    <col min="4614" max="4614" width="10.109375" style="17" customWidth="1"/>
-    <col min="4615" max="4615" width="8.88671875" style="17"/>
-    <col min="4616" max="4616" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="4617" max="4864" width="8.88671875" style="17"/>
-    <col min="4865" max="4865" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4866" max="4866" width="11.77734375" style="17" customWidth="1"/>
-    <col min="4867" max="4867" width="10.33203125" style="17" customWidth="1"/>
-    <col min="4868" max="4868" width="12.33203125" style="17" customWidth="1"/>
-    <col min="4869" max="4869" width="8.88671875" style="17"/>
-    <col min="4870" max="4870" width="10.109375" style="17" customWidth="1"/>
-    <col min="4871" max="4871" width="8.88671875" style="17"/>
-    <col min="4872" max="4872" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="4873" max="5120" width="8.88671875" style="17"/>
-    <col min="5121" max="5121" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="5122" max="5122" width="11.77734375" style="17" customWidth="1"/>
-    <col min="5123" max="5123" width="10.33203125" style="17" customWidth="1"/>
-    <col min="5124" max="5124" width="12.33203125" style="17" customWidth="1"/>
-    <col min="5125" max="5125" width="8.88671875" style="17"/>
-    <col min="5126" max="5126" width="10.109375" style="17" customWidth="1"/>
-    <col min="5127" max="5127" width="8.88671875" style="17"/>
-    <col min="5128" max="5128" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="5129" max="5376" width="8.88671875" style="17"/>
-    <col min="5377" max="5377" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="5378" max="5378" width="11.77734375" style="17" customWidth="1"/>
-    <col min="5379" max="5379" width="10.33203125" style="17" customWidth="1"/>
-    <col min="5380" max="5380" width="12.33203125" style="17" customWidth="1"/>
-    <col min="5381" max="5381" width="8.88671875" style="17"/>
-    <col min="5382" max="5382" width="10.109375" style="17" customWidth="1"/>
-    <col min="5383" max="5383" width="8.88671875" style="17"/>
-    <col min="5384" max="5384" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="5385" max="5632" width="8.88671875" style="17"/>
-    <col min="5633" max="5633" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="5634" max="5634" width="11.77734375" style="17" customWidth="1"/>
-    <col min="5635" max="5635" width="10.33203125" style="17" customWidth="1"/>
-    <col min="5636" max="5636" width="12.33203125" style="17" customWidth="1"/>
-    <col min="5637" max="5637" width="8.88671875" style="17"/>
-    <col min="5638" max="5638" width="10.109375" style="17" customWidth="1"/>
-    <col min="5639" max="5639" width="8.88671875" style="17"/>
-    <col min="5640" max="5640" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="5641" max="5888" width="8.88671875" style="17"/>
-    <col min="5889" max="5889" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="5890" max="5890" width="11.77734375" style="17" customWidth="1"/>
-    <col min="5891" max="5891" width="10.33203125" style="17" customWidth="1"/>
-    <col min="5892" max="5892" width="12.33203125" style="17" customWidth="1"/>
-    <col min="5893" max="5893" width="8.88671875" style="17"/>
-    <col min="5894" max="5894" width="10.109375" style="17" customWidth="1"/>
-    <col min="5895" max="5895" width="8.88671875" style="17"/>
-    <col min="5896" max="5896" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="5897" max="6144" width="8.88671875" style="17"/>
-    <col min="6145" max="6145" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="6146" max="6146" width="11.77734375" style="17" customWidth="1"/>
-    <col min="6147" max="6147" width="10.33203125" style="17" customWidth="1"/>
-    <col min="6148" max="6148" width="12.33203125" style="17" customWidth="1"/>
-    <col min="6149" max="6149" width="8.88671875" style="17"/>
-    <col min="6150" max="6150" width="10.109375" style="17" customWidth="1"/>
-    <col min="6151" max="6151" width="8.88671875" style="17"/>
-    <col min="6152" max="6152" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="6153" max="6400" width="8.88671875" style="17"/>
-    <col min="6401" max="6401" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="6402" max="6402" width="11.77734375" style="17" customWidth="1"/>
-    <col min="6403" max="6403" width="10.33203125" style="17" customWidth="1"/>
-    <col min="6404" max="6404" width="12.33203125" style="17" customWidth="1"/>
-    <col min="6405" max="6405" width="8.88671875" style="17"/>
-    <col min="6406" max="6406" width="10.109375" style="17" customWidth="1"/>
-    <col min="6407" max="6407" width="8.88671875" style="17"/>
-    <col min="6408" max="6408" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="6409" max="6656" width="8.88671875" style="17"/>
-    <col min="6657" max="6657" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="6658" max="6658" width="11.77734375" style="17" customWidth="1"/>
-    <col min="6659" max="6659" width="10.33203125" style="17" customWidth="1"/>
-    <col min="6660" max="6660" width="12.33203125" style="17" customWidth="1"/>
-    <col min="6661" max="6661" width="8.88671875" style="17"/>
-    <col min="6662" max="6662" width="10.109375" style="17" customWidth="1"/>
-    <col min="6663" max="6663" width="8.88671875" style="17"/>
-    <col min="6664" max="6664" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="6665" max="6912" width="8.88671875" style="17"/>
-    <col min="6913" max="6913" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="6914" max="6914" width="11.77734375" style="17" customWidth="1"/>
-    <col min="6915" max="6915" width="10.33203125" style="17" customWidth="1"/>
-    <col min="6916" max="6916" width="12.33203125" style="17" customWidth="1"/>
-    <col min="6917" max="6917" width="8.88671875" style="17"/>
-    <col min="6918" max="6918" width="10.109375" style="17" customWidth="1"/>
-    <col min="6919" max="6919" width="8.88671875" style="17"/>
-    <col min="6920" max="6920" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="6921" max="7168" width="8.88671875" style="17"/>
-    <col min="7169" max="7169" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7170" max="7170" width="11.77734375" style="17" customWidth="1"/>
-    <col min="7171" max="7171" width="10.33203125" style="17" customWidth="1"/>
-    <col min="7172" max="7172" width="12.33203125" style="17" customWidth="1"/>
-    <col min="7173" max="7173" width="8.88671875" style="17"/>
-    <col min="7174" max="7174" width="10.109375" style="17" customWidth="1"/>
-    <col min="7175" max="7175" width="8.88671875" style="17"/>
-    <col min="7176" max="7176" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="7177" max="7424" width="8.88671875" style="17"/>
-    <col min="7425" max="7425" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7426" max="7426" width="11.77734375" style="17" customWidth="1"/>
-    <col min="7427" max="7427" width="10.33203125" style="17" customWidth="1"/>
-    <col min="7428" max="7428" width="12.33203125" style="17" customWidth="1"/>
-    <col min="7429" max="7429" width="8.88671875" style="17"/>
-    <col min="7430" max="7430" width="10.109375" style="17" customWidth="1"/>
-    <col min="7431" max="7431" width="8.88671875" style="17"/>
-    <col min="7432" max="7432" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="7433" max="7680" width="8.88671875" style="17"/>
-    <col min="7681" max="7681" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7682" max="7682" width="11.77734375" style="17" customWidth="1"/>
-    <col min="7683" max="7683" width="10.33203125" style="17" customWidth="1"/>
-    <col min="7684" max="7684" width="12.33203125" style="17" customWidth="1"/>
-    <col min="7685" max="7685" width="8.88671875" style="17"/>
-    <col min="7686" max="7686" width="10.109375" style="17" customWidth="1"/>
-    <col min="7687" max="7687" width="8.88671875" style="17"/>
-    <col min="7688" max="7688" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="7689" max="7936" width="8.88671875" style="17"/>
-    <col min="7937" max="7937" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7938" max="7938" width="11.77734375" style="17" customWidth="1"/>
-    <col min="7939" max="7939" width="10.33203125" style="17" customWidth="1"/>
-    <col min="7940" max="7940" width="12.33203125" style="17" customWidth="1"/>
-    <col min="7941" max="7941" width="8.88671875" style="17"/>
-    <col min="7942" max="7942" width="10.109375" style="17" customWidth="1"/>
-    <col min="7943" max="7943" width="8.88671875" style="17"/>
-    <col min="7944" max="7944" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="7945" max="8192" width="8.88671875" style="17"/>
-    <col min="8193" max="8193" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="8194" max="8194" width="11.77734375" style="17" customWidth="1"/>
-    <col min="8195" max="8195" width="10.33203125" style="17" customWidth="1"/>
-    <col min="8196" max="8196" width="12.33203125" style="17" customWidth="1"/>
-    <col min="8197" max="8197" width="8.88671875" style="17"/>
-    <col min="8198" max="8198" width="10.109375" style="17" customWidth="1"/>
-    <col min="8199" max="8199" width="8.88671875" style="17"/>
-    <col min="8200" max="8200" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="8201" max="8448" width="8.88671875" style="17"/>
-    <col min="8449" max="8449" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="8450" max="8450" width="11.77734375" style="17" customWidth="1"/>
-    <col min="8451" max="8451" width="10.33203125" style="17" customWidth="1"/>
-    <col min="8452" max="8452" width="12.33203125" style="17" customWidth="1"/>
-    <col min="8453" max="8453" width="8.88671875" style="17"/>
-    <col min="8454" max="8454" width="10.109375" style="17" customWidth="1"/>
-    <col min="8455" max="8455" width="8.88671875" style="17"/>
-    <col min="8456" max="8456" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="8457" max="8704" width="8.88671875" style="17"/>
-    <col min="8705" max="8705" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="8706" max="8706" width="11.77734375" style="17" customWidth="1"/>
-    <col min="8707" max="8707" width="10.33203125" style="17" customWidth="1"/>
-    <col min="8708" max="8708" width="12.33203125" style="17" customWidth="1"/>
-    <col min="8709" max="8709" width="8.88671875" style="17"/>
-    <col min="8710" max="8710" width="10.109375" style="17" customWidth="1"/>
-    <col min="8711" max="8711" width="8.88671875" style="17"/>
-    <col min="8712" max="8712" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="8713" max="8960" width="8.88671875" style="17"/>
-    <col min="8961" max="8961" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="8962" max="8962" width="11.77734375" style="17" customWidth="1"/>
-    <col min="8963" max="8963" width="10.33203125" style="17" customWidth="1"/>
-    <col min="8964" max="8964" width="12.33203125" style="17" customWidth="1"/>
-    <col min="8965" max="8965" width="8.88671875" style="17"/>
-    <col min="8966" max="8966" width="10.109375" style="17" customWidth="1"/>
-    <col min="8967" max="8967" width="8.88671875" style="17"/>
-    <col min="8968" max="8968" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="8969" max="9216" width="8.88671875" style="17"/>
-    <col min="9217" max="9217" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="9218" max="9218" width="11.77734375" style="17" customWidth="1"/>
-    <col min="9219" max="9219" width="10.33203125" style="17" customWidth="1"/>
-    <col min="9220" max="9220" width="12.33203125" style="17" customWidth="1"/>
-    <col min="9221" max="9221" width="8.88671875" style="17"/>
-    <col min="9222" max="9222" width="10.109375" style="17" customWidth="1"/>
-    <col min="9223" max="9223" width="8.88671875" style="17"/>
-    <col min="9224" max="9224" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9225" max="9472" width="8.88671875" style="17"/>
-    <col min="9473" max="9473" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="9474" max="9474" width="11.77734375" style="17" customWidth="1"/>
-    <col min="9475" max="9475" width="10.33203125" style="17" customWidth="1"/>
-    <col min="9476" max="9476" width="12.33203125" style="17" customWidth="1"/>
-    <col min="9477" max="9477" width="8.88671875" style="17"/>
-    <col min="9478" max="9478" width="10.109375" style="17" customWidth="1"/>
-    <col min="9479" max="9479" width="8.88671875" style="17"/>
-    <col min="9480" max="9480" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9481" max="9728" width="8.88671875" style="17"/>
-    <col min="9729" max="9729" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="9730" max="9730" width="11.77734375" style="17" customWidth="1"/>
-    <col min="9731" max="9731" width="10.33203125" style="17" customWidth="1"/>
-    <col min="9732" max="9732" width="12.33203125" style="17" customWidth="1"/>
-    <col min="9733" max="9733" width="8.88671875" style="17"/>
-    <col min="9734" max="9734" width="10.109375" style="17" customWidth="1"/>
-    <col min="9735" max="9735" width="8.88671875" style="17"/>
-    <col min="9736" max="9736" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9737" max="9984" width="8.88671875" style="17"/>
-    <col min="9985" max="9985" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="9986" max="9986" width="11.77734375" style="17" customWidth="1"/>
-    <col min="9987" max="9987" width="10.33203125" style="17" customWidth="1"/>
-    <col min="9988" max="9988" width="12.33203125" style="17" customWidth="1"/>
-    <col min="9989" max="9989" width="8.88671875" style="17"/>
-    <col min="9990" max="9990" width="10.109375" style="17" customWidth="1"/>
-    <col min="9991" max="9991" width="8.88671875" style="17"/>
-    <col min="9992" max="9992" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9993" max="10240" width="8.88671875" style="17"/>
-    <col min="10241" max="10241" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="10242" max="10242" width="11.77734375" style="17" customWidth="1"/>
-    <col min="10243" max="10243" width="10.33203125" style="17" customWidth="1"/>
-    <col min="10244" max="10244" width="12.33203125" style="17" customWidth="1"/>
-    <col min="10245" max="10245" width="8.88671875" style="17"/>
-    <col min="10246" max="10246" width="10.109375" style="17" customWidth="1"/>
-    <col min="10247" max="10247" width="8.88671875" style="17"/>
-    <col min="10248" max="10248" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="10249" max="10496" width="8.88671875" style="17"/>
-    <col min="10497" max="10497" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="10498" max="10498" width="11.77734375" style="17" customWidth="1"/>
-    <col min="10499" max="10499" width="10.33203125" style="17" customWidth="1"/>
-    <col min="10500" max="10500" width="12.33203125" style="17" customWidth="1"/>
-    <col min="10501" max="10501" width="8.88671875" style="17"/>
-    <col min="10502" max="10502" width="10.109375" style="17" customWidth="1"/>
-    <col min="10503" max="10503" width="8.88671875" style="17"/>
-    <col min="10504" max="10504" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="10505" max="10752" width="8.88671875" style="17"/>
-    <col min="10753" max="10753" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="10754" max="10754" width="11.77734375" style="17" customWidth="1"/>
-    <col min="10755" max="10755" width="10.33203125" style="17" customWidth="1"/>
-    <col min="10756" max="10756" width="12.33203125" style="17" customWidth="1"/>
-    <col min="10757" max="10757" width="8.88671875" style="17"/>
-    <col min="10758" max="10758" width="10.109375" style="17" customWidth="1"/>
-    <col min="10759" max="10759" width="8.88671875" style="17"/>
-    <col min="10760" max="10760" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="10761" max="11008" width="8.88671875" style="17"/>
-    <col min="11009" max="11009" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="11010" max="11010" width="11.77734375" style="17" customWidth="1"/>
-    <col min="11011" max="11011" width="10.33203125" style="17" customWidth="1"/>
-    <col min="11012" max="11012" width="12.33203125" style="17" customWidth="1"/>
-    <col min="11013" max="11013" width="8.88671875" style="17"/>
-    <col min="11014" max="11014" width="10.109375" style="17" customWidth="1"/>
-    <col min="11015" max="11015" width="8.88671875" style="17"/>
-    <col min="11016" max="11016" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="11017" max="11264" width="8.88671875" style="17"/>
-    <col min="11265" max="11265" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="11266" max="11266" width="11.77734375" style="17" customWidth="1"/>
-    <col min="11267" max="11267" width="10.33203125" style="17" customWidth="1"/>
-    <col min="11268" max="11268" width="12.33203125" style="17" customWidth="1"/>
-    <col min="11269" max="11269" width="8.88671875" style="17"/>
-    <col min="11270" max="11270" width="10.109375" style="17" customWidth="1"/>
-    <col min="11271" max="11271" width="8.88671875" style="17"/>
-    <col min="11272" max="11272" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="11273" max="11520" width="8.88671875" style="17"/>
-    <col min="11521" max="11521" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="11522" max="11522" width="11.77734375" style="17" customWidth="1"/>
-    <col min="11523" max="11523" width="10.33203125" style="17" customWidth="1"/>
-    <col min="11524" max="11524" width="12.33203125" style="17" customWidth="1"/>
-    <col min="11525" max="11525" width="8.88671875" style="17"/>
-    <col min="11526" max="11526" width="10.109375" style="17" customWidth="1"/>
-    <col min="11527" max="11527" width="8.88671875" style="17"/>
-    <col min="11528" max="11528" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="11529" max="11776" width="8.88671875" style="17"/>
-    <col min="11777" max="11777" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="11778" max="11778" width="11.77734375" style="17" customWidth="1"/>
-    <col min="11779" max="11779" width="10.33203125" style="17" customWidth="1"/>
-    <col min="11780" max="11780" width="12.33203125" style="17" customWidth="1"/>
-    <col min="11781" max="11781" width="8.88671875" style="17"/>
-    <col min="11782" max="11782" width="10.109375" style="17" customWidth="1"/>
-    <col min="11783" max="11783" width="8.88671875" style="17"/>
-    <col min="11784" max="11784" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="11785" max="12032" width="8.88671875" style="17"/>
-    <col min="12033" max="12033" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="12034" max="12034" width="11.77734375" style="17" customWidth="1"/>
-    <col min="12035" max="12035" width="10.33203125" style="17" customWidth="1"/>
-    <col min="12036" max="12036" width="12.33203125" style="17" customWidth="1"/>
-    <col min="12037" max="12037" width="8.88671875" style="17"/>
-    <col min="12038" max="12038" width="10.109375" style="17" customWidth="1"/>
-    <col min="12039" max="12039" width="8.88671875" style="17"/>
-    <col min="12040" max="12040" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="12041" max="12288" width="8.88671875" style="17"/>
-    <col min="12289" max="12289" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="12290" max="12290" width="11.77734375" style="17" customWidth="1"/>
-    <col min="12291" max="12291" width="10.33203125" style="17" customWidth="1"/>
-    <col min="12292" max="12292" width="12.33203125" style="17" customWidth="1"/>
-    <col min="12293" max="12293" width="8.88671875" style="17"/>
-    <col min="12294" max="12294" width="10.109375" style="17" customWidth="1"/>
-    <col min="12295" max="12295" width="8.88671875" style="17"/>
-    <col min="12296" max="12296" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="12297" max="12544" width="8.88671875" style="17"/>
-    <col min="12545" max="12545" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="12546" max="12546" width="11.77734375" style="17" customWidth="1"/>
-    <col min="12547" max="12547" width="10.33203125" style="17" customWidth="1"/>
-    <col min="12548" max="12548" width="12.33203125" style="17" customWidth="1"/>
-    <col min="12549" max="12549" width="8.88671875" style="17"/>
-    <col min="12550" max="12550" width="10.109375" style="17" customWidth="1"/>
-    <col min="12551" max="12551" width="8.88671875" style="17"/>
-    <col min="12552" max="12552" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="12553" max="12800" width="8.88671875" style="17"/>
-    <col min="12801" max="12801" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="12802" max="12802" width="11.77734375" style="17" customWidth="1"/>
-    <col min="12803" max="12803" width="10.33203125" style="17" customWidth="1"/>
-    <col min="12804" max="12804" width="12.33203125" style="17" customWidth="1"/>
-    <col min="12805" max="12805" width="8.88671875" style="17"/>
-    <col min="12806" max="12806" width="10.109375" style="17" customWidth="1"/>
-    <col min="12807" max="12807" width="8.88671875" style="17"/>
-    <col min="12808" max="12808" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="12809" max="13056" width="8.88671875" style="17"/>
-    <col min="13057" max="13057" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="13058" max="13058" width="11.77734375" style="17" customWidth="1"/>
-    <col min="13059" max="13059" width="10.33203125" style="17" customWidth="1"/>
-    <col min="13060" max="13060" width="12.33203125" style="17" customWidth="1"/>
-    <col min="13061" max="13061" width="8.88671875" style="17"/>
-    <col min="13062" max="13062" width="10.109375" style="17" customWidth="1"/>
-    <col min="13063" max="13063" width="8.88671875" style="17"/>
-    <col min="13064" max="13064" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="13065" max="13312" width="8.88671875" style="17"/>
-    <col min="13313" max="13313" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="13314" max="13314" width="11.77734375" style="17" customWidth="1"/>
-    <col min="13315" max="13315" width="10.33203125" style="17" customWidth="1"/>
-    <col min="13316" max="13316" width="12.33203125" style="17" customWidth="1"/>
-    <col min="13317" max="13317" width="8.88671875" style="17"/>
-    <col min="13318" max="13318" width="10.109375" style="17" customWidth="1"/>
-    <col min="13319" max="13319" width="8.88671875" style="17"/>
-    <col min="13320" max="13320" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="13321" max="13568" width="8.88671875" style="17"/>
-    <col min="13569" max="13569" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="13570" max="13570" width="11.77734375" style="17" customWidth="1"/>
-    <col min="13571" max="13571" width="10.33203125" style="17" customWidth="1"/>
-    <col min="13572" max="13572" width="12.33203125" style="17" customWidth="1"/>
-    <col min="13573" max="13573" width="8.88671875" style="17"/>
-    <col min="13574" max="13574" width="10.109375" style="17" customWidth="1"/>
-    <col min="13575" max="13575" width="8.88671875" style="17"/>
-    <col min="13576" max="13576" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="13577" max="13824" width="8.88671875" style="17"/>
-    <col min="13825" max="13825" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="13826" max="13826" width="11.77734375" style="17" customWidth="1"/>
-    <col min="13827" max="13827" width="10.33203125" style="17" customWidth="1"/>
-    <col min="13828" max="13828" width="12.33203125" style="17" customWidth="1"/>
-    <col min="13829" max="13829" width="8.88671875" style="17"/>
-    <col min="13830" max="13830" width="10.109375" style="17" customWidth="1"/>
-    <col min="13831" max="13831" width="8.88671875" style="17"/>
-    <col min="13832" max="13832" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="13833" max="14080" width="8.88671875" style="17"/>
-    <col min="14081" max="14081" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="14082" max="14082" width="11.77734375" style="17" customWidth="1"/>
-    <col min="14083" max="14083" width="10.33203125" style="17" customWidth="1"/>
-    <col min="14084" max="14084" width="12.33203125" style="17" customWidth="1"/>
-    <col min="14085" max="14085" width="8.88671875" style="17"/>
-    <col min="14086" max="14086" width="10.109375" style="17" customWidth="1"/>
-    <col min="14087" max="14087" width="8.88671875" style="17"/>
-    <col min="14088" max="14088" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="14089" max="14336" width="8.88671875" style="17"/>
-    <col min="14337" max="14337" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="14338" max="14338" width="11.77734375" style="17" customWidth="1"/>
-    <col min="14339" max="14339" width="10.33203125" style="17" customWidth="1"/>
-    <col min="14340" max="14340" width="12.33203125" style="17" customWidth="1"/>
-    <col min="14341" max="14341" width="8.88671875" style="17"/>
-    <col min="14342" max="14342" width="10.109375" style="17" customWidth="1"/>
-    <col min="14343" max="14343" width="8.88671875" style="17"/>
-    <col min="14344" max="14344" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="14345" max="14592" width="8.88671875" style="17"/>
-    <col min="14593" max="14593" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="14594" max="14594" width="11.77734375" style="17" customWidth="1"/>
-    <col min="14595" max="14595" width="10.33203125" style="17" customWidth="1"/>
-    <col min="14596" max="14596" width="12.33203125" style="17" customWidth="1"/>
-    <col min="14597" max="14597" width="8.88671875" style="17"/>
-    <col min="14598" max="14598" width="10.109375" style="17" customWidth="1"/>
-    <col min="14599" max="14599" width="8.88671875" style="17"/>
-    <col min="14600" max="14600" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="14601" max="14848" width="8.88671875" style="17"/>
-    <col min="14849" max="14849" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="14850" max="14850" width="11.77734375" style="17" customWidth="1"/>
-    <col min="14851" max="14851" width="10.33203125" style="17" customWidth="1"/>
-    <col min="14852" max="14852" width="12.33203125" style="17" customWidth="1"/>
-    <col min="14853" max="14853" width="8.88671875" style="17"/>
-    <col min="14854" max="14854" width="10.109375" style="17" customWidth="1"/>
-    <col min="14855" max="14855" width="8.88671875" style="17"/>
-    <col min="14856" max="14856" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="14857" max="15104" width="8.88671875" style="17"/>
-    <col min="15105" max="15105" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="15106" max="15106" width="11.77734375" style="17" customWidth="1"/>
-    <col min="15107" max="15107" width="10.33203125" style="17" customWidth="1"/>
-    <col min="15108" max="15108" width="12.33203125" style="17" customWidth="1"/>
-    <col min="15109" max="15109" width="8.88671875" style="17"/>
-    <col min="15110" max="15110" width="10.109375" style="17" customWidth="1"/>
-    <col min="15111" max="15111" width="8.88671875" style="17"/>
-    <col min="15112" max="15112" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="15113" max="15360" width="8.88671875" style="17"/>
-    <col min="15361" max="15361" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="15362" max="15362" width="11.77734375" style="17" customWidth="1"/>
-    <col min="15363" max="15363" width="10.33203125" style="17" customWidth="1"/>
-    <col min="15364" max="15364" width="12.33203125" style="17" customWidth="1"/>
-    <col min="15365" max="15365" width="8.88671875" style="17"/>
-    <col min="15366" max="15366" width="10.109375" style="17" customWidth="1"/>
-    <col min="15367" max="15367" width="8.88671875" style="17"/>
-    <col min="15368" max="15368" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="15369" max="15616" width="8.88671875" style="17"/>
-    <col min="15617" max="15617" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="15618" max="15618" width="11.77734375" style="17" customWidth="1"/>
-    <col min="15619" max="15619" width="10.33203125" style="17" customWidth="1"/>
-    <col min="15620" max="15620" width="12.33203125" style="17" customWidth="1"/>
-    <col min="15621" max="15621" width="8.88671875" style="17"/>
-    <col min="15622" max="15622" width="10.109375" style="17" customWidth="1"/>
-    <col min="15623" max="15623" width="8.88671875" style="17"/>
-    <col min="15624" max="15624" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="15625" max="15872" width="8.88671875" style="17"/>
-    <col min="15873" max="15873" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="15874" max="15874" width="11.77734375" style="17" customWidth="1"/>
-    <col min="15875" max="15875" width="10.33203125" style="17" customWidth="1"/>
-    <col min="15876" max="15876" width="12.33203125" style="17" customWidth="1"/>
-    <col min="15877" max="15877" width="8.88671875" style="17"/>
-    <col min="15878" max="15878" width="10.109375" style="17" customWidth="1"/>
-    <col min="15879" max="15879" width="8.88671875" style="17"/>
-    <col min="15880" max="15880" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="15881" max="16128" width="8.88671875" style="17"/>
-    <col min="16129" max="16129" width="12.88671875" style="17" bestFit="1" customWidth="1"/>
-    <col min="16130" max="16130" width="11.77734375" style="17" customWidth="1"/>
-    <col min="16131" max="16131" width="10.33203125" style="17" customWidth="1"/>
-    <col min="16132" max="16132" width="12.33203125" style="17" customWidth="1"/>
-    <col min="16133" max="16133" width="8.88671875" style="17"/>
-    <col min="16134" max="16134" width="10.109375" style="17" customWidth="1"/>
-    <col min="16135" max="16135" width="8.88671875" style="17"/>
-    <col min="16136" max="16136" width="9.77734375" style="17" bestFit="1" customWidth="1"/>
-    <col min="16137" max="16384" width="8.88671875" style="17"/>
+    <col min="1" max="1" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="16" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="16"/>
+    <col min="6" max="6" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="16"/>
+    <col min="8" max="8" width="43" style="16" customWidth="1"/>
+    <col min="9" max="11" width="8.85546875" style="16"/>
+    <col min="12" max="12" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.85546875" style="16"/>
+    <col min="15" max="15" width="43.28515625" style="16" customWidth="1"/>
+    <col min="16" max="18" width="8.85546875" style="16"/>
+    <col min="19" max="19" width="12.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="256" width="8.85546875" style="16"/>
+    <col min="257" max="257" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="11.7109375" style="16" customWidth="1"/>
+    <col min="259" max="259" width="10.28515625" style="16" customWidth="1"/>
+    <col min="260" max="260" width="12.28515625" style="16" customWidth="1"/>
+    <col min="261" max="261" width="8.85546875" style="16"/>
+    <col min="262" max="262" width="10.140625" style="16" customWidth="1"/>
+    <col min="263" max="263" width="8.85546875" style="16"/>
+    <col min="264" max="264" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="265" max="512" width="8.85546875" style="16"/>
+    <col min="513" max="513" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="11.7109375" style="16" customWidth="1"/>
+    <col min="515" max="515" width="10.28515625" style="16" customWidth="1"/>
+    <col min="516" max="516" width="12.28515625" style="16" customWidth="1"/>
+    <col min="517" max="517" width="8.85546875" style="16"/>
+    <col min="518" max="518" width="10.140625" style="16" customWidth="1"/>
+    <col min="519" max="519" width="8.85546875" style="16"/>
+    <col min="520" max="520" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="521" max="768" width="8.85546875" style="16"/>
+    <col min="769" max="769" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="770" max="770" width="11.7109375" style="16" customWidth="1"/>
+    <col min="771" max="771" width="10.28515625" style="16" customWidth="1"/>
+    <col min="772" max="772" width="12.28515625" style="16" customWidth="1"/>
+    <col min="773" max="773" width="8.85546875" style="16"/>
+    <col min="774" max="774" width="10.140625" style="16" customWidth="1"/>
+    <col min="775" max="775" width="8.85546875" style="16"/>
+    <col min="776" max="776" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="777" max="1024" width="8.85546875" style="16"/>
+    <col min="1025" max="1025" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="1026" max="1026" width="11.7109375" style="16" customWidth="1"/>
+    <col min="1027" max="1027" width="10.28515625" style="16" customWidth="1"/>
+    <col min="1028" max="1028" width="12.28515625" style="16" customWidth="1"/>
+    <col min="1029" max="1029" width="8.85546875" style="16"/>
+    <col min="1030" max="1030" width="10.140625" style="16" customWidth="1"/>
+    <col min="1031" max="1031" width="8.85546875" style="16"/>
+    <col min="1032" max="1032" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="1033" max="1280" width="8.85546875" style="16"/>
+    <col min="1281" max="1281" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="1282" max="1282" width="11.7109375" style="16" customWidth="1"/>
+    <col min="1283" max="1283" width="10.28515625" style="16" customWidth="1"/>
+    <col min="1284" max="1284" width="12.28515625" style="16" customWidth="1"/>
+    <col min="1285" max="1285" width="8.85546875" style="16"/>
+    <col min="1286" max="1286" width="10.140625" style="16" customWidth="1"/>
+    <col min="1287" max="1287" width="8.85546875" style="16"/>
+    <col min="1288" max="1288" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="1289" max="1536" width="8.85546875" style="16"/>
+    <col min="1537" max="1537" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="1538" max="1538" width="11.7109375" style="16" customWidth="1"/>
+    <col min="1539" max="1539" width="10.28515625" style="16" customWidth="1"/>
+    <col min="1540" max="1540" width="12.28515625" style="16" customWidth="1"/>
+    <col min="1541" max="1541" width="8.85546875" style="16"/>
+    <col min="1542" max="1542" width="10.140625" style="16" customWidth="1"/>
+    <col min="1543" max="1543" width="8.85546875" style="16"/>
+    <col min="1544" max="1544" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="1545" max="1792" width="8.85546875" style="16"/>
+    <col min="1793" max="1793" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="1794" max="1794" width="11.7109375" style="16" customWidth="1"/>
+    <col min="1795" max="1795" width="10.28515625" style="16" customWidth="1"/>
+    <col min="1796" max="1796" width="12.28515625" style="16" customWidth="1"/>
+    <col min="1797" max="1797" width="8.85546875" style="16"/>
+    <col min="1798" max="1798" width="10.140625" style="16" customWidth="1"/>
+    <col min="1799" max="1799" width="8.85546875" style="16"/>
+    <col min="1800" max="1800" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="1801" max="2048" width="8.85546875" style="16"/>
+    <col min="2049" max="2049" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2050" max="2050" width="11.7109375" style="16" customWidth="1"/>
+    <col min="2051" max="2051" width="10.28515625" style="16" customWidth="1"/>
+    <col min="2052" max="2052" width="12.28515625" style="16" customWidth="1"/>
+    <col min="2053" max="2053" width="8.85546875" style="16"/>
+    <col min="2054" max="2054" width="10.140625" style="16" customWidth="1"/>
+    <col min="2055" max="2055" width="8.85546875" style="16"/>
+    <col min="2056" max="2056" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2057" max="2304" width="8.85546875" style="16"/>
+    <col min="2305" max="2305" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2306" max="2306" width="11.7109375" style="16" customWidth="1"/>
+    <col min="2307" max="2307" width="10.28515625" style="16" customWidth="1"/>
+    <col min="2308" max="2308" width="12.28515625" style="16" customWidth="1"/>
+    <col min="2309" max="2309" width="8.85546875" style="16"/>
+    <col min="2310" max="2310" width="10.140625" style="16" customWidth="1"/>
+    <col min="2311" max="2311" width="8.85546875" style="16"/>
+    <col min="2312" max="2312" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2313" max="2560" width="8.85546875" style="16"/>
+    <col min="2561" max="2561" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2562" max="2562" width="11.7109375" style="16" customWidth="1"/>
+    <col min="2563" max="2563" width="10.28515625" style="16" customWidth="1"/>
+    <col min="2564" max="2564" width="12.28515625" style="16" customWidth="1"/>
+    <col min="2565" max="2565" width="8.85546875" style="16"/>
+    <col min="2566" max="2566" width="10.140625" style="16" customWidth="1"/>
+    <col min="2567" max="2567" width="8.85546875" style="16"/>
+    <col min="2568" max="2568" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2569" max="2816" width="8.85546875" style="16"/>
+    <col min="2817" max="2817" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2818" max="2818" width="11.7109375" style="16" customWidth="1"/>
+    <col min="2819" max="2819" width="10.28515625" style="16" customWidth="1"/>
+    <col min="2820" max="2820" width="12.28515625" style="16" customWidth="1"/>
+    <col min="2821" max="2821" width="8.85546875" style="16"/>
+    <col min="2822" max="2822" width="10.140625" style="16" customWidth="1"/>
+    <col min="2823" max="2823" width="8.85546875" style="16"/>
+    <col min="2824" max="2824" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2825" max="3072" width="8.85546875" style="16"/>
+    <col min="3073" max="3073" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3074" max="3074" width="11.7109375" style="16" customWidth="1"/>
+    <col min="3075" max="3075" width="10.28515625" style="16" customWidth="1"/>
+    <col min="3076" max="3076" width="12.28515625" style="16" customWidth="1"/>
+    <col min="3077" max="3077" width="8.85546875" style="16"/>
+    <col min="3078" max="3078" width="10.140625" style="16" customWidth="1"/>
+    <col min="3079" max="3079" width="8.85546875" style="16"/>
+    <col min="3080" max="3080" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="3081" max="3328" width="8.85546875" style="16"/>
+    <col min="3329" max="3329" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3330" max="3330" width="11.7109375" style="16" customWidth="1"/>
+    <col min="3331" max="3331" width="10.28515625" style="16" customWidth="1"/>
+    <col min="3332" max="3332" width="12.28515625" style="16" customWidth="1"/>
+    <col min="3333" max="3333" width="8.85546875" style="16"/>
+    <col min="3334" max="3334" width="10.140625" style="16" customWidth="1"/>
+    <col min="3335" max="3335" width="8.85546875" style="16"/>
+    <col min="3336" max="3336" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="3337" max="3584" width="8.85546875" style="16"/>
+    <col min="3585" max="3585" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3586" max="3586" width="11.7109375" style="16" customWidth="1"/>
+    <col min="3587" max="3587" width="10.28515625" style="16" customWidth="1"/>
+    <col min="3588" max="3588" width="12.28515625" style="16" customWidth="1"/>
+    <col min="3589" max="3589" width="8.85546875" style="16"/>
+    <col min="3590" max="3590" width="10.140625" style="16" customWidth="1"/>
+    <col min="3591" max="3591" width="8.85546875" style="16"/>
+    <col min="3592" max="3592" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="3593" max="3840" width="8.85546875" style="16"/>
+    <col min="3841" max="3841" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3842" max="3842" width="11.7109375" style="16" customWidth="1"/>
+    <col min="3843" max="3843" width="10.28515625" style="16" customWidth="1"/>
+    <col min="3844" max="3844" width="12.28515625" style="16" customWidth="1"/>
+    <col min="3845" max="3845" width="8.85546875" style="16"/>
+    <col min="3846" max="3846" width="10.140625" style="16" customWidth="1"/>
+    <col min="3847" max="3847" width="8.85546875" style="16"/>
+    <col min="3848" max="3848" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="3849" max="4096" width="8.85546875" style="16"/>
+    <col min="4097" max="4097" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="4098" max="4098" width="11.7109375" style="16" customWidth="1"/>
+    <col min="4099" max="4099" width="10.28515625" style="16" customWidth="1"/>
+    <col min="4100" max="4100" width="12.28515625" style="16" customWidth="1"/>
+    <col min="4101" max="4101" width="8.85546875" style="16"/>
+    <col min="4102" max="4102" width="10.140625" style="16" customWidth="1"/>
+    <col min="4103" max="4103" width="8.85546875" style="16"/>
+    <col min="4104" max="4104" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4105" max="4352" width="8.85546875" style="16"/>
+    <col min="4353" max="4353" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="4354" max="4354" width="11.7109375" style="16" customWidth="1"/>
+    <col min="4355" max="4355" width="10.28515625" style="16" customWidth="1"/>
+    <col min="4356" max="4356" width="12.28515625" style="16" customWidth="1"/>
+    <col min="4357" max="4357" width="8.85546875" style="16"/>
+    <col min="4358" max="4358" width="10.140625" style="16" customWidth="1"/>
+    <col min="4359" max="4359" width="8.85546875" style="16"/>
+    <col min="4360" max="4360" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4361" max="4608" width="8.85546875" style="16"/>
+    <col min="4609" max="4609" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="4610" max="4610" width="11.7109375" style="16" customWidth="1"/>
+    <col min="4611" max="4611" width="10.28515625" style="16" customWidth="1"/>
+    <col min="4612" max="4612" width="12.28515625" style="16" customWidth="1"/>
+    <col min="4613" max="4613" width="8.85546875" style="16"/>
+    <col min="4614" max="4614" width="10.140625" style="16" customWidth="1"/>
+    <col min="4615" max="4615" width="8.85546875" style="16"/>
+    <col min="4616" max="4616" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4617" max="4864" width="8.85546875" style="16"/>
+    <col min="4865" max="4865" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="4866" max="4866" width="11.7109375" style="16" customWidth="1"/>
+    <col min="4867" max="4867" width="10.28515625" style="16" customWidth="1"/>
+    <col min="4868" max="4868" width="12.28515625" style="16" customWidth="1"/>
+    <col min="4869" max="4869" width="8.85546875" style="16"/>
+    <col min="4870" max="4870" width="10.140625" style="16" customWidth="1"/>
+    <col min="4871" max="4871" width="8.85546875" style="16"/>
+    <col min="4872" max="4872" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4873" max="5120" width="8.85546875" style="16"/>
+    <col min="5121" max="5121" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="5122" max="5122" width="11.7109375" style="16" customWidth="1"/>
+    <col min="5123" max="5123" width="10.28515625" style="16" customWidth="1"/>
+    <col min="5124" max="5124" width="12.28515625" style="16" customWidth="1"/>
+    <col min="5125" max="5125" width="8.85546875" style="16"/>
+    <col min="5126" max="5126" width="10.140625" style="16" customWidth="1"/>
+    <col min="5127" max="5127" width="8.85546875" style="16"/>
+    <col min="5128" max="5128" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="5129" max="5376" width="8.85546875" style="16"/>
+    <col min="5377" max="5377" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="5378" max="5378" width="11.7109375" style="16" customWidth="1"/>
+    <col min="5379" max="5379" width="10.28515625" style="16" customWidth="1"/>
+    <col min="5380" max="5380" width="12.28515625" style="16" customWidth="1"/>
+    <col min="5381" max="5381" width="8.85546875" style="16"/>
+    <col min="5382" max="5382" width="10.140625" style="16" customWidth="1"/>
+    <col min="5383" max="5383" width="8.85546875" style="16"/>
+    <col min="5384" max="5384" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="5385" max="5632" width="8.85546875" style="16"/>
+    <col min="5633" max="5633" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="5634" max="5634" width="11.7109375" style="16" customWidth="1"/>
+    <col min="5635" max="5635" width="10.28515625" style="16" customWidth="1"/>
+    <col min="5636" max="5636" width="12.28515625" style="16" customWidth="1"/>
+    <col min="5637" max="5637" width="8.85546875" style="16"/>
+    <col min="5638" max="5638" width="10.140625" style="16" customWidth="1"/>
+    <col min="5639" max="5639" width="8.85546875" style="16"/>
+    <col min="5640" max="5640" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="5641" max="5888" width="8.85546875" style="16"/>
+    <col min="5889" max="5889" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="5890" max="5890" width="11.7109375" style="16" customWidth="1"/>
+    <col min="5891" max="5891" width="10.28515625" style="16" customWidth="1"/>
+    <col min="5892" max="5892" width="12.28515625" style="16" customWidth="1"/>
+    <col min="5893" max="5893" width="8.85546875" style="16"/>
+    <col min="5894" max="5894" width="10.140625" style="16" customWidth="1"/>
+    <col min="5895" max="5895" width="8.85546875" style="16"/>
+    <col min="5896" max="5896" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="5897" max="6144" width="8.85546875" style="16"/>
+    <col min="6145" max="6145" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="6146" max="6146" width="11.7109375" style="16" customWidth="1"/>
+    <col min="6147" max="6147" width="10.28515625" style="16" customWidth="1"/>
+    <col min="6148" max="6148" width="12.28515625" style="16" customWidth="1"/>
+    <col min="6149" max="6149" width="8.85546875" style="16"/>
+    <col min="6150" max="6150" width="10.140625" style="16" customWidth="1"/>
+    <col min="6151" max="6151" width="8.85546875" style="16"/>
+    <col min="6152" max="6152" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="6153" max="6400" width="8.85546875" style="16"/>
+    <col min="6401" max="6401" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="6402" max="6402" width="11.7109375" style="16" customWidth="1"/>
+    <col min="6403" max="6403" width="10.28515625" style="16" customWidth="1"/>
+    <col min="6404" max="6404" width="12.28515625" style="16" customWidth="1"/>
+    <col min="6405" max="6405" width="8.85546875" style="16"/>
+    <col min="6406" max="6406" width="10.140625" style="16" customWidth="1"/>
+    <col min="6407" max="6407" width="8.85546875" style="16"/>
+    <col min="6408" max="6408" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="6409" max="6656" width="8.85546875" style="16"/>
+    <col min="6657" max="6657" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="6658" max="6658" width="11.7109375" style="16" customWidth="1"/>
+    <col min="6659" max="6659" width="10.28515625" style="16" customWidth="1"/>
+    <col min="6660" max="6660" width="12.28515625" style="16" customWidth="1"/>
+    <col min="6661" max="6661" width="8.85546875" style="16"/>
+    <col min="6662" max="6662" width="10.140625" style="16" customWidth="1"/>
+    <col min="6663" max="6663" width="8.85546875" style="16"/>
+    <col min="6664" max="6664" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="6665" max="6912" width="8.85546875" style="16"/>
+    <col min="6913" max="6913" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="6914" max="6914" width="11.7109375" style="16" customWidth="1"/>
+    <col min="6915" max="6915" width="10.28515625" style="16" customWidth="1"/>
+    <col min="6916" max="6916" width="12.28515625" style="16" customWidth="1"/>
+    <col min="6917" max="6917" width="8.85546875" style="16"/>
+    <col min="6918" max="6918" width="10.140625" style="16" customWidth="1"/>
+    <col min="6919" max="6919" width="8.85546875" style="16"/>
+    <col min="6920" max="6920" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="6921" max="7168" width="8.85546875" style="16"/>
+    <col min="7169" max="7169" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7170" max="7170" width="11.7109375" style="16" customWidth="1"/>
+    <col min="7171" max="7171" width="10.28515625" style="16" customWidth="1"/>
+    <col min="7172" max="7172" width="12.28515625" style="16" customWidth="1"/>
+    <col min="7173" max="7173" width="8.85546875" style="16"/>
+    <col min="7174" max="7174" width="10.140625" style="16" customWidth="1"/>
+    <col min="7175" max="7175" width="8.85546875" style="16"/>
+    <col min="7176" max="7176" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7177" max="7424" width="8.85546875" style="16"/>
+    <col min="7425" max="7425" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7426" max="7426" width="11.7109375" style="16" customWidth="1"/>
+    <col min="7427" max="7427" width="10.28515625" style="16" customWidth="1"/>
+    <col min="7428" max="7428" width="12.28515625" style="16" customWidth="1"/>
+    <col min="7429" max="7429" width="8.85546875" style="16"/>
+    <col min="7430" max="7430" width="10.140625" style="16" customWidth="1"/>
+    <col min="7431" max="7431" width="8.85546875" style="16"/>
+    <col min="7432" max="7432" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7433" max="7680" width="8.85546875" style="16"/>
+    <col min="7681" max="7681" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7682" max="7682" width="11.7109375" style="16" customWidth="1"/>
+    <col min="7683" max="7683" width="10.28515625" style="16" customWidth="1"/>
+    <col min="7684" max="7684" width="12.28515625" style="16" customWidth="1"/>
+    <col min="7685" max="7685" width="8.85546875" style="16"/>
+    <col min="7686" max="7686" width="10.140625" style="16" customWidth="1"/>
+    <col min="7687" max="7687" width="8.85546875" style="16"/>
+    <col min="7688" max="7688" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7689" max="7936" width="8.85546875" style="16"/>
+    <col min="7937" max="7937" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7938" max="7938" width="11.7109375" style="16" customWidth="1"/>
+    <col min="7939" max="7939" width="10.28515625" style="16" customWidth="1"/>
+    <col min="7940" max="7940" width="12.28515625" style="16" customWidth="1"/>
+    <col min="7941" max="7941" width="8.85546875" style="16"/>
+    <col min="7942" max="7942" width="10.140625" style="16" customWidth="1"/>
+    <col min="7943" max="7943" width="8.85546875" style="16"/>
+    <col min="7944" max="7944" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7945" max="8192" width="8.85546875" style="16"/>
+    <col min="8193" max="8193" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="8194" max="8194" width="11.7109375" style="16" customWidth="1"/>
+    <col min="8195" max="8195" width="10.28515625" style="16" customWidth="1"/>
+    <col min="8196" max="8196" width="12.28515625" style="16" customWidth="1"/>
+    <col min="8197" max="8197" width="8.85546875" style="16"/>
+    <col min="8198" max="8198" width="10.140625" style="16" customWidth="1"/>
+    <col min="8199" max="8199" width="8.85546875" style="16"/>
+    <col min="8200" max="8200" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="8201" max="8448" width="8.85546875" style="16"/>
+    <col min="8449" max="8449" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="8450" max="8450" width="11.7109375" style="16" customWidth="1"/>
+    <col min="8451" max="8451" width="10.28515625" style="16" customWidth="1"/>
+    <col min="8452" max="8452" width="12.28515625" style="16" customWidth="1"/>
+    <col min="8453" max="8453" width="8.85546875" style="16"/>
+    <col min="8454" max="8454" width="10.140625" style="16" customWidth="1"/>
+    <col min="8455" max="8455" width="8.85546875" style="16"/>
+    <col min="8456" max="8456" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="8457" max="8704" width="8.85546875" style="16"/>
+    <col min="8705" max="8705" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="8706" max="8706" width="11.7109375" style="16" customWidth="1"/>
+    <col min="8707" max="8707" width="10.28515625" style="16" customWidth="1"/>
+    <col min="8708" max="8708" width="12.28515625" style="16" customWidth="1"/>
+    <col min="8709" max="8709" width="8.85546875" style="16"/>
+    <col min="8710" max="8710" width="10.140625" style="16" customWidth="1"/>
+    <col min="8711" max="8711" width="8.85546875" style="16"/>
+    <col min="8712" max="8712" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="8713" max="8960" width="8.85546875" style="16"/>
+    <col min="8961" max="8961" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="8962" max="8962" width="11.7109375" style="16" customWidth="1"/>
+    <col min="8963" max="8963" width="10.28515625" style="16" customWidth="1"/>
+    <col min="8964" max="8964" width="12.28515625" style="16" customWidth="1"/>
+    <col min="8965" max="8965" width="8.85546875" style="16"/>
+    <col min="8966" max="8966" width="10.140625" style="16" customWidth="1"/>
+    <col min="8967" max="8967" width="8.85546875" style="16"/>
+    <col min="8968" max="8968" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="8969" max="9216" width="8.85546875" style="16"/>
+    <col min="9217" max="9217" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9218" max="9218" width="11.7109375" style="16" customWidth="1"/>
+    <col min="9219" max="9219" width="10.28515625" style="16" customWidth="1"/>
+    <col min="9220" max="9220" width="12.28515625" style="16" customWidth="1"/>
+    <col min="9221" max="9221" width="8.85546875" style="16"/>
+    <col min="9222" max="9222" width="10.140625" style="16" customWidth="1"/>
+    <col min="9223" max="9223" width="8.85546875" style="16"/>
+    <col min="9224" max="9224" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="9225" max="9472" width="8.85546875" style="16"/>
+    <col min="9473" max="9473" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9474" max="9474" width="11.7109375" style="16" customWidth="1"/>
+    <col min="9475" max="9475" width="10.28515625" style="16" customWidth="1"/>
+    <col min="9476" max="9476" width="12.28515625" style="16" customWidth="1"/>
+    <col min="9477" max="9477" width="8.85546875" style="16"/>
+    <col min="9478" max="9478" width="10.140625" style="16" customWidth="1"/>
+    <col min="9479" max="9479" width="8.85546875" style="16"/>
+    <col min="9480" max="9480" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="9481" max="9728" width="8.85546875" style="16"/>
+    <col min="9729" max="9729" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9730" max="9730" width="11.7109375" style="16" customWidth="1"/>
+    <col min="9731" max="9731" width="10.28515625" style="16" customWidth="1"/>
+    <col min="9732" max="9732" width="12.28515625" style="16" customWidth="1"/>
+    <col min="9733" max="9733" width="8.85546875" style="16"/>
+    <col min="9734" max="9734" width="10.140625" style="16" customWidth="1"/>
+    <col min="9735" max="9735" width="8.85546875" style="16"/>
+    <col min="9736" max="9736" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="9737" max="9984" width="8.85546875" style="16"/>
+    <col min="9985" max="9985" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9986" max="9986" width="11.7109375" style="16" customWidth="1"/>
+    <col min="9987" max="9987" width="10.28515625" style="16" customWidth="1"/>
+    <col min="9988" max="9988" width="12.28515625" style="16" customWidth="1"/>
+    <col min="9989" max="9989" width="8.85546875" style="16"/>
+    <col min="9990" max="9990" width="10.140625" style="16" customWidth="1"/>
+    <col min="9991" max="9991" width="8.85546875" style="16"/>
+    <col min="9992" max="9992" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="9993" max="10240" width="8.85546875" style="16"/>
+    <col min="10241" max="10241" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="10242" max="10242" width="11.7109375" style="16" customWidth="1"/>
+    <col min="10243" max="10243" width="10.28515625" style="16" customWidth="1"/>
+    <col min="10244" max="10244" width="12.28515625" style="16" customWidth="1"/>
+    <col min="10245" max="10245" width="8.85546875" style="16"/>
+    <col min="10246" max="10246" width="10.140625" style="16" customWidth="1"/>
+    <col min="10247" max="10247" width="8.85546875" style="16"/>
+    <col min="10248" max="10248" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="10249" max="10496" width="8.85546875" style="16"/>
+    <col min="10497" max="10497" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="10498" max="10498" width="11.7109375" style="16" customWidth="1"/>
+    <col min="10499" max="10499" width="10.28515625" style="16" customWidth="1"/>
+    <col min="10500" max="10500" width="12.28515625" style="16" customWidth="1"/>
+    <col min="10501" max="10501" width="8.85546875" style="16"/>
+    <col min="10502" max="10502" width="10.140625" style="16" customWidth="1"/>
+    <col min="10503" max="10503" width="8.85546875" style="16"/>
+    <col min="10504" max="10504" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="10505" max="10752" width="8.85546875" style="16"/>
+    <col min="10753" max="10753" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="10754" max="10754" width="11.7109375" style="16" customWidth="1"/>
+    <col min="10755" max="10755" width="10.28515625" style="16" customWidth="1"/>
+    <col min="10756" max="10756" width="12.28515625" style="16" customWidth="1"/>
+    <col min="10757" max="10757" width="8.85546875" style="16"/>
+    <col min="10758" max="10758" width="10.140625" style="16" customWidth="1"/>
+    <col min="10759" max="10759" width="8.85546875" style="16"/>
+    <col min="10760" max="10760" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="10761" max="11008" width="8.85546875" style="16"/>
+    <col min="11009" max="11009" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11010" max="11010" width="11.7109375" style="16" customWidth="1"/>
+    <col min="11011" max="11011" width="10.28515625" style="16" customWidth="1"/>
+    <col min="11012" max="11012" width="12.28515625" style="16" customWidth="1"/>
+    <col min="11013" max="11013" width="8.85546875" style="16"/>
+    <col min="11014" max="11014" width="10.140625" style="16" customWidth="1"/>
+    <col min="11015" max="11015" width="8.85546875" style="16"/>
+    <col min="11016" max="11016" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="11017" max="11264" width="8.85546875" style="16"/>
+    <col min="11265" max="11265" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11266" max="11266" width="11.7109375" style="16" customWidth="1"/>
+    <col min="11267" max="11267" width="10.28515625" style="16" customWidth="1"/>
+    <col min="11268" max="11268" width="12.28515625" style="16" customWidth="1"/>
+    <col min="11269" max="11269" width="8.85546875" style="16"/>
+    <col min="11270" max="11270" width="10.140625" style="16" customWidth="1"/>
+    <col min="11271" max="11271" width="8.85546875" style="16"/>
+    <col min="11272" max="11272" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="11273" max="11520" width="8.85546875" style="16"/>
+    <col min="11521" max="11521" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11522" max="11522" width="11.7109375" style="16" customWidth="1"/>
+    <col min="11523" max="11523" width="10.28515625" style="16" customWidth="1"/>
+    <col min="11524" max="11524" width="12.28515625" style="16" customWidth="1"/>
+    <col min="11525" max="11525" width="8.85546875" style="16"/>
+    <col min="11526" max="11526" width="10.140625" style="16" customWidth="1"/>
+    <col min="11527" max="11527" width="8.85546875" style="16"/>
+    <col min="11528" max="11528" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="11529" max="11776" width="8.85546875" style="16"/>
+    <col min="11777" max="11777" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11778" max="11778" width="11.7109375" style="16" customWidth="1"/>
+    <col min="11779" max="11779" width="10.28515625" style="16" customWidth="1"/>
+    <col min="11780" max="11780" width="12.28515625" style="16" customWidth="1"/>
+    <col min="11781" max="11781" width="8.85546875" style="16"/>
+    <col min="11782" max="11782" width="10.140625" style="16" customWidth="1"/>
+    <col min="11783" max="11783" width="8.85546875" style="16"/>
+    <col min="11784" max="11784" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="11785" max="12032" width="8.85546875" style="16"/>
+    <col min="12033" max="12033" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12034" max="12034" width="11.7109375" style="16" customWidth="1"/>
+    <col min="12035" max="12035" width="10.28515625" style="16" customWidth="1"/>
+    <col min="12036" max="12036" width="12.28515625" style="16" customWidth="1"/>
+    <col min="12037" max="12037" width="8.85546875" style="16"/>
+    <col min="12038" max="12038" width="10.140625" style="16" customWidth="1"/>
+    <col min="12039" max="12039" width="8.85546875" style="16"/>
+    <col min="12040" max="12040" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="12041" max="12288" width="8.85546875" style="16"/>
+    <col min="12289" max="12289" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12290" max="12290" width="11.7109375" style="16" customWidth="1"/>
+    <col min="12291" max="12291" width="10.28515625" style="16" customWidth="1"/>
+    <col min="12292" max="12292" width="12.28515625" style="16" customWidth="1"/>
+    <col min="12293" max="12293" width="8.85546875" style="16"/>
+    <col min="12294" max="12294" width="10.140625" style="16" customWidth="1"/>
+    <col min="12295" max="12295" width="8.85546875" style="16"/>
+    <col min="12296" max="12296" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="12297" max="12544" width="8.85546875" style="16"/>
+    <col min="12545" max="12545" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12546" max="12546" width="11.7109375" style="16" customWidth="1"/>
+    <col min="12547" max="12547" width="10.28515625" style="16" customWidth="1"/>
+    <col min="12548" max="12548" width="12.28515625" style="16" customWidth="1"/>
+    <col min="12549" max="12549" width="8.85546875" style="16"/>
+    <col min="12550" max="12550" width="10.140625" style="16" customWidth="1"/>
+    <col min="12551" max="12551" width="8.85546875" style="16"/>
+    <col min="12552" max="12552" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="12553" max="12800" width="8.85546875" style="16"/>
+    <col min="12801" max="12801" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12802" max="12802" width="11.7109375" style="16" customWidth="1"/>
+    <col min="12803" max="12803" width="10.28515625" style="16" customWidth="1"/>
+    <col min="12804" max="12804" width="12.28515625" style="16" customWidth="1"/>
+    <col min="12805" max="12805" width="8.85546875" style="16"/>
+    <col min="12806" max="12806" width="10.140625" style="16" customWidth="1"/>
+    <col min="12807" max="12807" width="8.85546875" style="16"/>
+    <col min="12808" max="12808" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="12809" max="13056" width="8.85546875" style="16"/>
+    <col min="13057" max="13057" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13058" max="13058" width="11.7109375" style="16" customWidth="1"/>
+    <col min="13059" max="13059" width="10.28515625" style="16" customWidth="1"/>
+    <col min="13060" max="13060" width="12.28515625" style="16" customWidth="1"/>
+    <col min="13061" max="13061" width="8.85546875" style="16"/>
+    <col min="13062" max="13062" width="10.140625" style="16" customWidth="1"/>
+    <col min="13063" max="13063" width="8.85546875" style="16"/>
+    <col min="13064" max="13064" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="13065" max="13312" width="8.85546875" style="16"/>
+    <col min="13313" max="13313" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13314" max="13314" width="11.7109375" style="16" customWidth="1"/>
+    <col min="13315" max="13315" width="10.28515625" style="16" customWidth="1"/>
+    <col min="13316" max="13316" width="12.28515625" style="16" customWidth="1"/>
+    <col min="13317" max="13317" width="8.85546875" style="16"/>
+    <col min="13318" max="13318" width="10.140625" style="16" customWidth="1"/>
+    <col min="13319" max="13319" width="8.85546875" style="16"/>
+    <col min="13320" max="13320" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="13321" max="13568" width="8.85546875" style="16"/>
+    <col min="13569" max="13569" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13570" max="13570" width="11.7109375" style="16" customWidth="1"/>
+    <col min="13571" max="13571" width="10.28515625" style="16" customWidth="1"/>
+    <col min="13572" max="13572" width="12.28515625" style="16" customWidth="1"/>
+    <col min="13573" max="13573" width="8.85546875" style="16"/>
+    <col min="13574" max="13574" width="10.140625" style="16" customWidth="1"/>
+    <col min="13575" max="13575" width="8.85546875" style="16"/>
+    <col min="13576" max="13576" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="13577" max="13824" width="8.85546875" style="16"/>
+    <col min="13825" max="13825" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13826" max="13826" width="11.7109375" style="16" customWidth="1"/>
+    <col min="13827" max="13827" width="10.28515625" style="16" customWidth="1"/>
+    <col min="13828" max="13828" width="12.28515625" style="16" customWidth="1"/>
+    <col min="13829" max="13829" width="8.85546875" style="16"/>
+    <col min="13830" max="13830" width="10.140625" style="16" customWidth="1"/>
+    <col min="13831" max="13831" width="8.85546875" style="16"/>
+    <col min="13832" max="13832" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="13833" max="14080" width="8.85546875" style="16"/>
+    <col min="14081" max="14081" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="14082" max="14082" width="11.7109375" style="16" customWidth="1"/>
+    <col min="14083" max="14083" width="10.28515625" style="16" customWidth="1"/>
+    <col min="14084" max="14084" width="12.28515625" style="16" customWidth="1"/>
+    <col min="14085" max="14085" width="8.85546875" style="16"/>
+    <col min="14086" max="14086" width="10.140625" style="16" customWidth="1"/>
+    <col min="14087" max="14087" width="8.85546875" style="16"/>
+    <col min="14088" max="14088" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="14089" max="14336" width="8.85546875" style="16"/>
+    <col min="14337" max="14337" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="14338" max="14338" width="11.7109375" style="16" customWidth="1"/>
+    <col min="14339" max="14339" width="10.28515625" style="16" customWidth="1"/>
+    <col min="14340" max="14340" width="12.28515625" style="16" customWidth="1"/>
+    <col min="14341" max="14341" width="8.85546875" style="16"/>
+    <col min="14342" max="14342" width="10.140625" style="16" customWidth="1"/>
+    <col min="14343" max="14343" width="8.85546875" style="16"/>
+    <col min="14344" max="14344" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="14345" max="14592" width="8.85546875" style="16"/>
+    <col min="14593" max="14593" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="14594" max="14594" width="11.7109375" style="16" customWidth="1"/>
+    <col min="14595" max="14595" width="10.28515625" style="16" customWidth="1"/>
+    <col min="14596" max="14596" width="12.28515625" style="16" customWidth="1"/>
+    <col min="14597" max="14597" width="8.85546875" style="16"/>
+    <col min="14598" max="14598" width="10.140625" style="16" customWidth="1"/>
+    <col min="14599" max="14599" width="8.85546875" style="16"/>
+    <col min="14600" max="14600" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="14601" max="14848" width="8.85546875" style="16"/>
+    <col min="14849" max="14849" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="14850" max="14850" width="11.7109375" style="16" customWidth="1"/>
+    <col min="14851" max="14851" width="10.28515625" style="16" customWidth="1"/>
+    <col min="14852" max="14852" width="12.28515625" style="16" customWidth="1"/>
+    <col min="14853" max="14853" width="8.85546875" style="16"/>
+    <col min="14854" max="14854" width="10.140625" style="16" customWidth="1"/>
+    <col min="14855" max="14855" width="8.85546875" style="16"/>
+    <col min="14856" max="14856" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="14857" max="15104" width="8.85546875" style="16"/>
+    <col min="15105" max="15105" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="15106" max="15106" width="11.7109375" style="16" customWidth="1"/>
+    <col min="15107" max="15107" width="10.28515625" style="16" customWidth="1"/>
+    <col min="15108" max="15108" width="12.28515625" style="16" customWidth="1"/>
+    <col min="15109" max="15109" width="8.85546875" style="16"/>
+    <col min="15110" max="15110" width="10.140625" style="16" customWidth="1"/>
+    <col min="15111" max="15111" width="8.85546875" style="16"/>
+    <col min="15112" max="15112" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="15113" max="15360" width="8.85546875" style="16"/>
+    <col min="15361" max="15361" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="15362" max="15362" width="11.7109375" style="16" customWidth="1"/>
+    <col min="15363" max="15363" width="10.28515625" style="16" customWidth="1"/>
+    <col min="15364" max="15364" width="12.28515625" style="16" customWidth="1"/>
+    <col min="15365" max="15365" width="8.85546875" style="16"/>
+    <col min="15366" max="15366" width="10.140625" style="16" customWidth="1"/>
+    <col min="15367" max="15367" width="8.85546875" style="16"/>
+    <col min="15368" max="15368" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="15369" max="15616" width="8.85546875" style="16"/>
+    <col min="15617" max="15617" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="15618" max="15618" width="11.7109375" style="16" customWidth="1"/>
+    <col min="15619" max="15619" width="10.28515625" style="16" customWidth="1"/>
+    <col min="15620" max="15620" width="12.28515625" style="16" customWidth="1"/>
+    <col min="15621" max="15621" width="8.85546875" style="16"/>
+    <col min="15622" max="15622" width="10.140625" style="16" customWidth="1"/>
+    <col min="15623" max="15623" width="8.85546875" style="16"/>
+    <col min="15624" max="15624" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="15625" max="15872" width="8.85546875" style="16"/>
+    <col min="15873" max="15873" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="15874" max="15874" width="11.7109375" style="16" customWidth="1"/>
+    <col min="15875" max="15875" width="10.28515625" style="16" customWidth="1"/>
+    <col min="15876" max="15876" width="12.28515625" style="16" customWidth="1"/>
+    <col min="15877" max="15877" width="8.85546875" style="16"/>
+    <col min="15878" max="15878" width="10.140625" style="16" customWidth="1"/>
+    <col min="15879" max="15879" width="8.85546875" style="16"/>
+    <col min="15880" max="15880" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="15881" max="16128" width="8.85546875" style="16"/>
+    <col min="16129" max="16129" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="16130" max="16130" width="11.7109375" style="16" customWidth="1"/>
+    <col min="16131" max="16131" width="10.28515625" style="16" customWidth="1"/>
+    <col min="16132" max="16132" width="12.28515625" style="16" customWidth="1"/>
+    <col min="16133" max="16133" width="8.85546875" style="16"/>
+    <col min="16134" max="16134" width="10.140625" style="16" customWidth="1"/>
+    <col min="16135" max="16135" width="8.85546875" style="16"/>
+    <col min="16136" max="16136" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="16137" max="16384" width="8.85546875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+    </row>
+    <row r="3" spans="1:12" ht="74.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="I3" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-    </row>
-    <row r="3" spans="1:12" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="I3" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-    </row>
-    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="20"/>
+      <c r="B4" s="19"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="K5" s="19" t="s">
+      <c r="J5" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="K5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="18" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="K6" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="K6" s="22" t="s">
+      <c r="L6" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="L6" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="K7" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="L7" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="L7" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="I8" s="23" t="s">
+      <c r="I8" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="J8" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="K8" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="L8" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="K9" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="L9" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="K10" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="L10" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="J11" s="26" t="s">
+      <c r="K11" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="K11" s="26" t="s">
+      <c r="L11" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="L11" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -6480,73 +7793,73 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="H15" s="26"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="27"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="H16" s="26"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="H16" s="27"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="H17" s="26"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="H17" s="27"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="H18" s="26"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="27"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="H19" s="26"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="H19" s="27"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="27"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H21" s="27"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H22" s="27"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H23" s="27"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H24" s="27"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H25" s="27"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H26" s="27"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H27" s="27"/>
+      <c r="H20" s="26"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H21" s="26"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H22" s="26"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H23" s="26"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H24" s="26"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H25" s="26"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H26" s="26"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H27" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Assignment 3 - Text , Logical, Date, Sumifs etc...xlsx
+++ b/Assignment 3 - Text , Logical, Date, Sumifs etc...xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Desktop\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95AC37F8-5294-47BF-8901-DF38A79ED50F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35B3308-D450-4819-9A2A-776E0FEA851D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6474,14 +6474,14 @@
       </c>
       <c r="C3" s="40">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>70</v>
       </c>
       <c r="G3" s="40">
         <f ca="1">TODAY()-14</f>
-        <v>46227</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
@@ -6490,14 +6490,14 @@
       </c>
       <c r="C4" s="41">
         <f ca="1">NOW()</f>
-        <v>46241.623535995372</v>
+        <v>46245.642577662038</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G4" s="41">
         <f ca="1">NOW()-14</f>
-        <v>46227.623535995372</v>
+        <v>46231.642577662038</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I7" s="43" t="str">
         <f ca="1">DATEDIF(C7,$C$3,"Y")&amp;" Years, "&amp;DATEDIF(C7,$C$3,"YM")&amp;" Months, "&amp;DATEDIF(C7,$C$3,"MD")&amp;" Days"</f>
-        <v>26 Years, 8 Months, 24 Days</v>
+        <v>26 Years, 8 Months, 28 Days</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="I8" s="43" t="str">
         <f t="shared" ref="I8:I18" ca="1" si="5">DATEDIF(C8,$C$3,"Y")&amp;" Years, "&amp;DATEDIF(C8,$C$3,"YM")&amp;" Months, "&amp;DATEDIF(C8,$C$3,"MD")&amp;" Days"</f>
-        <v>25 Years, 2 Months, 22 Days</v>
+        <v>25 Years, 2 Months, 26 Days</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="I9" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>22 Years, 8 Months, 17 Days</v>
+        <v>22 Years, 8 Months, 21 Days</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="I10" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>22 Years, 3 Months, 1 Days</v>
+        <v>22 Years, 3 Months, 5 Days</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="I11" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>21 Years, 4 Months, 0 Days</v>
+        <v>21 Years, 4 Months, 4 Days</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="I12" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>17 Years, 6 Months, 5 Days</v>
+        <v>17 Years, 6 Months, 9 Days</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="I13" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>16 Years, 2 Months, 6 Days</v>
+        <v>16 Years, 2 Months, 10 Days</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I14" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>15 Years, 8 Months, 25 Days</v>
+        <v>15 Years, 8 Months, 29 Days</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="I15" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>15 Years, 6 Months, 7 Days</v>
+        <v>15 Years, 6 Months, 11 Days</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="I16" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>13 Years, 3 Months, 1 Days</v>
+        <v>13 Years, 3 Months, 5 Days</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="I17" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>11 Years, 6 Months, 15 Days</v>
+        <v>11 Years, 6 Months, 19 Days</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="I18" s="43" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>11 Years, 3 Months, 8 Days</v>
+        <v>11 Years, 3 Months, 12 Days</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
